--- a/Input_data/EST_US_trad_eco_cal_2025-02-14_to_2025-02-25.xlsx
+++ b/Input_data/EST_US_trad_eco_cal_2025-02-14_to_2025-02-25.xlsx
@@ -1270,7 +1270,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>3-Month Bill Auction</t>
+          <t>6-Month Bill Auction</t>
         </is>
       </c>
       <c r="C35" t="inlineStr"/>
@@ -1288,7 +1288,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>6-Month Bill Auction</t>
+          <t>3-Month Bill Auction</t>
         </is>
       </c>
       <c r="C36" t="inlineStr"/>
@@ -1378,14 +1378,14 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Fed Barr Speech</t>
+          <t>52-Week Bill Auction</t>
         </is>
       </c>
       <c r="C41" t="inlineStr"/>
       <c r="D41" t="inlineStr"/>
       <c r="E41" t="inlineStr"/>
       <c r="F41" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="42">
@@ -1396,14 +1396,14 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>52-Week Bill Auction</t>
+          <t>Fed Barr Speech</t>
         </is>
       </c>
       <c r="C42" t="inlineStr"/>
       <c r="D42" t="inlineStr"/>
       <c r="E42" t="inlineStr"/>
       <c r="F42" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="43">
@@ -1540,14 +1540,14 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>MBA Purchase IndexFEB/14</t>
+          <t>MBA 30-Year Mortgage RateFEB/14</t>
         </is>
       </c>
       <c r="C50" t="inlineStr"/>
       <c r="D50" t="inlineStr"/>
       <c r="E50" t="inlineStr"/>
       <c r="F50" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="51">
@@ -1576,14 +1576,14 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>MBA 30-Year Mortgage RateFEB/14</t>
+          <t>MBA Mortgage ApplicationsFEB/14</t>
         </is>
       </c>
       <c r="C52" t="inlineStr"/>
       <c r="D52" t="inlineStr"/>
       <c r="E52" t="inlineStr"/>
       <c r="F52" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="53">
@@ -1684,7 +1684,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>MBA Mortgage Market IndexFEB/14</t>
+          <t>MBA Purchase IndexFEB/14</t>
         </is>
       </c>
       <c r="C58" t="inlineStr"/>
@@ -1702,7 +1702,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>MBA Mortgage ApplicationsFEB/14</t>
+          <t>MBA Mortgage Market IndexFEB/14</t>
         </is>
       </c>
       <c r="C59" t="inlineStr"/>
@@ -1838,22 +1838,18 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Housing StartsJAN</t>
+          <t>Building Permits MoM PrelJAN</t>
         </is>
       </c>
       <c r="C65" t="inlineStr"/>
-      <c r="D65" t="inlineStr">
-        <is>
-          <t>1.39M</t>
-        </is>
-      </c>
+      <c r="D65" t="inlineStr"/>
       <c r="E65" t="inlineStr">
         <is>
-          <t>1.35M</t>
+          <t>-0.8%</t>
         </is>
       </c>
       <c r="F65" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="66">
@@ -1864,18 +1860,22 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Building Permits MoM PrelJAN</t>
+          <t>Building Permits PrelJAN</t>
         </is>
       </c>
       <c r="C66" t="inlineStr"/>
-      <c r="D66" t="inlineStr"/>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>1.45M</t>
+        </is>
+      </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>-0.8%</t>
+          <t>1.47M</t>
         </is>
       </c>
       <c r="F66" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="67">
@@ -1886,18 +1886,18 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Building Permits PrelJAN</t>
+          <t>Housing StartsJAN</t>
         </is>
       </c>
       <c r="C67" t="inlineStr"/>
       <c r="D67" t="inlineStr">
         <is>
-          <t>1.45M</t>
+          <t>1.39M</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>1.47M</t>
+          <t>1.35M</t>
         </is>
       </c>
       <c r="F67" t="n">
@@ -2172,22 +2172,14 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Philadelphia Fed Manufacturing IndexFEB</t>
+          <t>Philly Fed New OrdersFEB</t>
         </is>
       </c>
       <c r="C82" t="inlineStr"/>
-      <c r="D82" t="inlineStr">
-        <is>
-          <t>25.5</t>
-        </is>
-      </c>
-      <c r="E82" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
+      <c r="D82" t="inlineStr"/>
+      <c r="E82" t="inlineStr"/>
       <c r="F82" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="83">
@@ -2198,22 +2190,14 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsFEB/15</t>
+          <t>Philly Fed Business ConditionsFEB</t>
         </is>
       </c>
       <c r="C83" t="inlineStr"/>
-      <c r="D83" t="inlineStr">
-        <is>
-          <t>216K</t>
-        </is>
-      </c>
-      <c r="E83" t="inlineStr">
-        <is>
-          <t>220.0K</t>
-        </is>
-      </c>
+      <c r="D83" t="inlineStr"/>
+      <c r="E83" t="inlineStr"/>
       <c r="F83" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="84">
@@ -2224,18 +2208,22 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageFEB/15</t>
+          <t>Initial Jobless ClaimsFEB/15</t>
         </is>
       </c>
       <c r="C84" t="inlineStr"/>
-      <c r="D84" t="inlineStr"/>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>216K</t>
+        </is>
+      </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>219.0K</t>
+          <t>220.0K</t>
         </is>
       </c>
       <c r="F84" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="85">
@@ -2246,14 +2234,22 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Philly Fed Business ConditionsFEB</t>
+          <t>Philadelphia Fed Manufacturing IndexFEB</t>
         </is>
       </c>
       <c r="C85" t="inlineStr"/>
-      <c r="D85" t="inlineStr"/>
-      <c r="E85" t="inlineStr"/>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>25.5</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
       <c r="F85" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="86">
@@ -2264,12 +2260,16 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Philly Fed CAPEX IndexFEB</t>
+          <t>Jobless Claims 4-week AverageFEB/15</t>
         </is>
       </c>
       <c r="C86" t="inlineStr"/>
       <c r="D86" t="inlineStr"/>
-      <c r="E86" t="inlineStr"/>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>219.0K</t>
+        </is>
+      </c>
       <c r="F86" t="n">
         <v>3</v>
       </c>
@@ -2282,7 +2282,7 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Philly Fed EmploymentFEB</t>
+          <t>Philly Fed CAPEX IndexFEB</t>
         </is>
       </c>
       <c r="C87" t="inlineStr"/>
@@ -2354,7 +2354,7 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Philly Fed New OrdersFEB</t>
+          <t>Philly Fed Prices PaidFEB</t>
         </is>
       </c>
       <c r="C91" t="inlineStr"/>
@@ -2504,12 +2504,16 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Philly Fed Prices PaidFEB</t>
+          <t>Continuing Jobless ClaimsFEB/08</t>
         </is>
       </c>
       <c r="C98" t="inlineStr"/>
       <c r="D98" t="inlineStr"/>
-      <c r="E98" t="inlineStr"/>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>1879.0K</t>
+        </is>
+      </c>
       <c r="F98" t="n">
         <v>3</v>
       </c>
@@ -2522,16 +2526,12 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsFEB/08</t>
+          <t>Philly Fed EmploymentFEB</t>
         </is>
       </c>
       <c r="C99" t="inlineStr"/>
       <c r="D99" t="inlineStr"/>
-      <c r="E99" t="inlineStr">
-        <is>
-          <t>1879.0K</t>
-        </is>
-      </c>
+      <c r="E99" t="inlineStr"/>
       <c r="F99" t="n">
         <v>3</v>
       </c>
@@ -2974,7 +2974,7 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeFEB/14</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C123" t="inlineStr"/>
@@ -2992,14 +2992,14 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeFEB/14</t>
+          <t>EIA Heating Oil Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C124" t="inlineStr"/>
       <c r="D124" t="inlineStr"/>
       <c r="E124" t="inlineStr"/>
       <c r="F124" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="125">
@@ -3010,14 +3010,14 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>15-Year Mortgage RateFEB/20</t>
+          <t>EIA Gasoline Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C125" t="inlineStr"/>
       <c r="D125" t="inlineStr"/>
       <c r="E125" t="inlineStr"/>
       <c r="F125" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="126">
@@ -3028,7 +3028,7 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeFEB/14</t>
+          <t>EIA Crude Oil Imports ChangeFEB/14</t>
         </is>
       </c>
       <c r="C126" t="inlineStr"/>
@@ -3046,7 +3046,7 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeFEB/14</t>
+          <t>EIA Distillate Fuel Production ChangeFEB/14</t>
         </is>
       </c>
       <c r="C127" t="inlineStr"/>
@@ -3064,7 +3064,7 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>30-Year Mortgage RateFEB/20</t>
+          <t>15-Year Mortgage RateFEB/20</t>
         </is>
       </c>
       <c r="C128" t="inlineStr"/>
@@ -3082,7 +3082,7 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeFEB/14</t>
+          <t>30-Year Mortgage RateFEB/20</t>
         </is>
       </c>
       <c r="C129" t="inlineStr"/>
@@ -3100,7 +3100,7 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeFEB/14</t>
+          <t>EIA Gasoline Production ChangeFEB/14</t>
         </is>
       </c>
       <c r="C130" t="inlineStr"/>
@@ -3118,7 +3118,7 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeFEB/14</t>
+          <t>EIA Distillate Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C131" t="inlineStr"/>
@@ -3382,7 +3382,7 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>S&amp;P Global Services PMI FlashFEB</t>
+          <t>S&amp;P Global Composite PMI FlashFEB</t>
         </is>
       </c>
       <c r="C145" t="inlineStr"/>
@@ -3426,7 +3426,7 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>S&amp;P Global Composite PMI FlashFEB</t>
+          <t>S&amp;P Global Services PMI FlashFEB</t>
         </is>
       </c>
       <c r="C147" t="inlineStr"/>
@@ -3626,18 +3626,22 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>Existing Home Sales MoMJAN</t>
+          <t>Michigan Inflation Expectations FinalFEB</t>
         </is>
       </c>
       <c r="C155" t="inlineStr"/>
-      <c r="D155" t="inlineStr"/>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>4.3%</t>
+        </is>
+      </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>-1.7%</t>
+          <t>4.3%</t>
         </is>
       </c>
       <c r="F155" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="156">
@@ -3648,22 +3652,22 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>Michigan Consumer Expectations FinalFEB</t>
+          <t>Existing Home SalesJAN</t>
         </is>
       </c>
       <c r="C156" t="inlineStr"/>
       <c r="D156" t="inlineStr">
         <is>
-          <t>67.3</t>
+          <t>4.17M</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>67.3</t>
+          <t>4.16M</t>
         </is>
       </c>
       <c r="F156" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="157">
@@ -3674,22 +3678,18 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>Michigan Inflation Expectations FinalFEB</t>
+          <t>Existing Home Sales MoMJAN</t>
         </is>
       </c>
       <c r="C157" t="inlineStr"/>
-      <c r="D157" t="inlineStr">
-        <is>
-          <t>4.3%</t>
-        </is>
-      </c>
+      <c r="D157" t="inlineStr"/>
       <c r="E157" t="inlineStr">
         <is>
-          <t>4.3%</t>
+          <t>-1.7%</t>
         </is>
       </c>
       <c r="F157" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="158">
@@ -3752,22 +3752,22 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>Existing Home SalesJAN</t>
+          <t>Michigan Consumer Expectations FinalFEB</t>
         </is>
       </c>
       <c r="C160" t="inlineStr"/>
       <c r="D160" t="inlineStr">
         <is>
-          <t>4.17M</t>
+          <t>67.3</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>4.16M</t>
+          <t>67.3</t>
         </is>
       </c>
       <c r="F160" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="161">
@@ -3840,7 +3840,7 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>Baker Hughes Oil Rig CountFEB/21</t>
+          <t>Baker Hughes Total Rigs CountFEB/21</t>
         </is>
       </c>
       <c r="C164" t="inlineStr"/>
@@ -3858,7 +3858,7 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>Baker Hughes Total Rigs CountFEB/21</t>
+          <t>Baker Hughes Oil Rig CountFEB/21</t>
         </is>
       </c>
       <c r="C165" t="inlineStr"/>
@@ -3984,7 +3984,7 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>3-Month Bill Auction</t>
+          <t>6-Month Bill Auction</t>
         </is>
       </c>
       <c r="C172" t="inlineStr"/>
@@ -4002,7 +4002,7 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>6-Month Bill Auction</t>
+          <t>3-Month Bill Auction</t>
         </is>
       </c>
       <c r="C173" t="inlineStr"/>

--- a/Input_data/EST_US_trad_eco_cal_2025-02-14_to_2025-02-25.xlsx
+++ b/Input_data/EST_US_trad_eco_cal_2025-02-14_to_2025-02-25.xlsx
@@ -722,26 +722,22 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Industrial Production MoMJAN</t>
+          <t>Manufacturing Production YoYJAN</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>0.5%</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+          <t>1%</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.8%</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="12">
@@ -752,22 +748,18 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Capacity UtilizationJAN</t>
+          <t>Industrial Production YoYJAN</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>77.8%</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>77.7%</t>
-        </is>
-      </c>
+          <t>2%</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>77.4%</t>
+          <t>0.9%</t>
         </is>
       </c>
       <c r="F12" t="n">
@@ -812,18 +804,22 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Industrial Production YoYJAN</t>
+          <t>Capacity UtilizationJAN</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>2%</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr"/>
+          <t>77.8%</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>77.7%</t>
+        </is>
+      </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>0.9%</t>
+          <t>77.4%</t>
         </is>
       </c>
       <c r="F14" t="n">
@@ -838,22 +834,26 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Manufacturing Production YoYJAN</t>
+          <t>Industrial Production MoMJAN</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>1%</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr"/>
+          <t>0.5%</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>0.8%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="16">
@@ -1234,7 +1234,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>6-Month Bill Auction</t>
+          <t>3-Month Bill Auction</t>
         </is>
       </c>
       <c r="C33" t="inlineStr"/>
@@ -1252,7 +1252,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>3-Month Bill Auction</t>
+          <t>6-Month Bill Auction</t>
         </is>
       </c>
       <c r="C34" t="inlineStr"/>
@@ -1522,7 +1522,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>MBA Mortgage Market IndexFEB/14</t>
+          <t>MBA Mortgage ApplicationsFEB/14</t>
         </is>
       </c>
       <c r="C49" t="inlineStr"/>
@@ -1594,7 +1594,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>MBA Mortgage ApplicationsFEB/14</t>
+          <t>MBA Mortgage Market IndexFEB/14</t>
         </is>
       </c>
       <c r="C53" t="inlineStr"/>
@@ -1746,22 +1746,18 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Building Permits PrelJAN</t>
+          <t>Building Permits MoM PrelJAN</t>
         </is>
       </c>
       <c r="C61" t="inlineStr"/>
-      <c r="D61" t="inlineStr">
-        <is>
-          <t>1.45M</t>
-        </is>
-      </c>
+      <c r="D61" t="inlineStr"/>
       <c r="E61" t="inlineStr">
         <is>
-          <t>1.47M</t>
+          <t>-0.8%</t>
         </is>
       </c>
       <c r="F61" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="62">
@@ -1846,18 +1842,22 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Building Permits MoM PrelJAN</t>
+          <t>Building Permits PrelJAN</t>
         </is>
       </c>
       <c r="C65" t="inlineStr"/>
-      <c r="D65" t="inlineStr"/>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>1.45M</t>
+        </is>
+      </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>-0.8%</t>
+          <t>1.47M</t>
         </is>
       </c>
       <c r="F65" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="66">
@@ -2202,14 +2202,22 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Philly Fed Business ConditionsFEB</t>
+          <t>Philadelphia Fed Manufacturing IndexFEB</t>
         </is>
       </c>
       <c r="C83" t="inlineStr"/>
-      <c r="D83" t="inlineStr"/>
-      <c r="E83" t="inlineStr"/>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>25.5</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
       <c r="F83" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="84">
@@ -2220,12 +2228,16 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Philly Fed New OrdersFEB</t>
+          <t>Continuing Jobless ClaimsFEB/08</t>
         </is>
       </c>
       <c r="C84" t="inlineStr"/>
       <c r="D84" t="inlineStr"/>
-      <c r="E84" t="inlineStr"/>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>1879.0K</t>
+        </is>
+      </c>
       <c r="F84" t="n">
         <v>3</v>
       </c>
@@ -2238,14 +2250,22 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Philly Fed Prices PaidFEB</t>
+          <t>Initial Jobless ClaimsFEB/15</t>
         </is>
       </c>
       <c r="C85" t="inlineStr"/>
-      <c r="D85" t="inlineStr"/>
-      <c r="E85" t="inlineStr"/>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>216K</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>220.0K</t>
+        </is>
+      </c>
       <c r="F85" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="86">
@@ -2256,22 +2276,18 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsFEB/15</t>
+          <t>Jobless Claims 4-week AverageFEB/15</t>
         </is>
       </c>
       <c r="C86" t="inlineStr"/>
-      <c r="D86" t="inlineStr">
-        <is>
-          <t>216K</t>
-        </is>
-      </c>
+      <c r="D86" t="inlineStr"/>
       <c r="E86" t="inlineStr">
         <is>
-          <t>220.0K</t>
+          <t>219.0K</t>
         </is>
       </c>
       <c r="F86" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="87">
@@ -2282,22 +2298,14 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Philadelphia Fed Manufacturing IndexFEB</t>
+          <t>Philly Fed Business ConditionsFEB</t>
         </is>
       </c>
       <c r="C87" t="inlineStr"/>
-      <c r="D87" t="inlineStr">
-        <is>
-          <t>25.5</t>
-        </is>
-      </c>
-      <c r="E87" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
+      <c r="D87" t="inlineStr"/>
+      <c r="E87" t="inlineStr"/>
       <c r="F87" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="88">
@@ -2308,16 +2316,12 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageFEB/15</t>
+          <t>Philly Fed CAPEX IndexFEB</t>
         </is>
       </c>
       <c r="C88" t="inlineStr"/>
       <c r="D88" t="inlineStr"/>
-      <c r="E88" t="inlineStr">
-        <is>
-          <t>219.0K</t>
-        </is>
-      </c>
+      <c r="E88" t="inlineStr"/>
       <c r="F88" t="n">
         <v>3</v>
       </c>
@@ -2330,16 +2334,12 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsFEB/08</t>
+          <t>Philly Fed New OrdersFEB</t>
         </is>
       </c>
       <c r="C89" t="inlineStr"/>
       <c r="D89" t="inlineStr"/>
-      <c r="E89" t="inlineStr">
-        <is>
-          <t>1879.0K</t>
-        </is>
-      </c>
+      <c r="E89" t="inlineStr"/>
       <c r="F89" t="n">
         <v>3</v>
       </c>
@@ -2352,7 +2352,7 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Philly Fed EmploymentFEB</t>
+          <t>Philly Fed Prices PaidFEB</t>
         </is>
       </c>
       <c r="C90" t="inlineStr"/>
@@ -2396,7 +2396,7 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Philly Fed CAPEX IndexFEB</t>
+          <t>Philly Fed EmploymentFEB</t>
         </is>
       </c>
       <c r="C92" t="inlineStr"/>
@@ -2668,7 +2668,7 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>4-Week Bill Auction</t>
+          <t>8-Week Bill Auction</t>
         </is>
       </c>
       <c r="C106" t="inlineStr"/>
@@ -2686,7 +2686,7 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>8-Week Bill Auction</t>
+          <t>4-Week Bill Auction</t>
         </is>
       </c>
       <c r="C107" t="inlineStr"/>
@@ -2812,7 +2812,7 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeFEB/14</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C114" t="inlineStr"/>
@@ -2830,7 +2830,7 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeFEB/14</t>
+          <t>30-Year Mortgage RateFEB/20</t>
         </is>
       </c>
       <c r="C115" t="inlineStr"/>
@@ -2848,7 +2848,7 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>30-Year Mortgage RateFEB/20</t>
+          <t>EIA Distillate Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C116" t="inlineStr"/>
@@ -2866,7 +2866,7 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>15-Year Mortgage RateFEB/20</t>
+          <t>EIA Gasoline Production ChangeFEB/14</t>
         </is>
       </c>
       <c r="C117" t="inlineStr"/>
@@ -2884,7 +2884,7 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeFEB/14</t>
+          <t>EIA Heating Oil Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C118" t="inlineStr"/>
@@ -2902,7 +2902,7 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeFEB/14</t>
+          <t>EIA Refinery Crude Runs ChangeFEB/14</t>
         </is>
       </c>
       <c r="C119" t="inlineStr"/>
@@ -2920,7 +2920,7 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeFEB/14</t>
+          <t>EIA Crude Oil Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C120" t="inlineStr"/>
@@ -2938,14 +2938,14 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeFEB/14</t>
+          <t>EIA Gasoline Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C121" t="inlineStr"/>
       <c r="D121" t="inlineStr"/>
       <c r="E121" t="inlineStr"/>
       <c r="F121" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="122">
@@ -2956,7 +2956,7 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeFEB/14</t>
+          <t>EIA Crude Oil Imports ChangeFEB/14</t>
         </is>
       </c>
       <c r="C122" t="inlineStr"/>
@@ -2974,14 +2974,14 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeFEB/14</t>
+          <t>EIA Distillate Fuel Production ChangeFEB/14</t>
         </is>
       </c>
       <c r="C123" t="inlineStr"/>
       <c r="D123" t="inlineStr"/>
       <c r="E123" t="inlineStr"/>
       <c r="F123" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="124">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeFEB/14</t>
+          <t>15-Year Mortgage RateFEB/20</t>
         </is>
       </c>
       <c r="C124" t="inlineStr"/>
@@ -3364,7 +3364,7 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>S&amp;P Global Services PMI FlashFEB</t>
+          <t>S&amp;P Global Composite PMI FlashFEB</t>
         </is>
       </c>
       <c r="C144" t="inlineStr"/>
@@ -3408,7 +3408,7 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>S&amp;P Global Composite PMI FlashFEB</t>
+          <t>S&amp;P Global Services PMI FlashFEB</t>
         </is>
       </c>
       <c r="C146" t="inlineStr"/>
@@ -3560,22 +3560,18 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Michigan Current Conditions FinalFEB</t>
+          <t>Existing Home Sales MoMJAN</t>
         </is>
       </c>
       <c r="C152" t="inlineStr"/>
-      <c r="D152" t="inlineStr">
-        <is>
-          <t>68.7</t>
-        </is>
-      </c>
+      <c r="D152" t="inlineStr"/>
       <c r="E152" t="inlineStr">
         <is>
-          <t>68.7</t>
+          <t>-1.7%</t>
         </is>
       </c>
       <c r="F152" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="153">
@@ -3586,18 +3582,18 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>Michigan Consumer Expectations FinalFEB</t>
+          <t>Michigan 5 Year Inflation Expectations FinalFEB</t>
         </is>
       </c>
       <c r="C153" t="inlineStr"/>
       <c r="D153" t="inlineStr">
         <is>
-          <t>67.3</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>67.3</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="F153" t="n">
@@ -3612,22 +3608,22 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>Michigan 5 Year Inflation Expectations FinalFEB</t>
+          <t>Existing Home SalesJAN</t>
         </is>
       </c>
       <c r="C154" t="inlineStr"/>
       <c r="D154" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>4.17M</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>4.16M</t>
         </is>
       </c>
       <c r="F154" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="155">
@@ -3664,18 +3660,22 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>Existing Home Sales MoMJAN</t>
+          <t>Michigan Consumer Expectations FinalFEB</t>
         </is>
       </c>
       <c r="C156" t="inlineStr"/>
-      <c r="D156" t="inlineStr"/>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>67.3</t>
+        </is>
+      </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>-1.7%</t>
+          <t>67.3</t>
         </is>
       </c>
       <c r="F156" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="157">
@@ -3686,22 +3686,22 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>Existing Home SalesJAN</t>
+          <t>Michigan Current Conditions FinalFEB</t>
         </is>
       </c>
       <c r="C157" t="inlineStr"/>
       <c r="D157" t="inlineStr">
         <is>
-          <t>4.17M</t>
+          <t>68.7</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>4.16M</t>
+          <t>68.7</t>
         </is>
       </c>
       <c r="F157" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="158">
@@ -3966,7 +3966,7 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>3-Month Bill Auction</t>
+          <t>6-Month Bill Auction</t>
         </is>
       </c>
       <c r="C171" t="inlineStr"/>
@@ -3984,7 +3984,7 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>6-Month Bill Auction</t>
+          <t>3-Month Bill Auction</t>
         </is>
       </c>
       <c r="C172" t="inlineStr"/>

--- a/Input_data/EST_US_trad_eco_cal_2025-02-14_to_2025-02-25.xlsx
+++ b/Input_data/EST_US_trad_eco_cal_2025-02-14_to_2025-02-25.xlsx
@@ -722,22 +722,26 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Manufacturing Production YoYJAN</t>
+          <t>Industrial Production MoMJAN</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>1%</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr"/>
+          <t>0.5%</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0.8%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="12">
@@ -748,18 +752,22 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Industrial Production YoYJAN</t>
+          <t>Capacity UtilizationJAN</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>2%</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr"/>
+          <t>77.8%</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>77.7%</t>
+        </is>
+      </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>0.9%</t>
+          <t>77.4%</t>
         </is>
       </c>
       <c r="F12" t="n">
@@ -804,22 +812,18 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Capacity UtilizationJAN</t>
+          <t>Industrial Production YoYJAN</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>77.8%</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>77.7%</t>
-        </is>
-      </c>
+          <t>2%</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
-          <t>77.4%</t>
+          <t>0.9%</t>
         </is>
       </c>
       <c r="F14" t="n">
@@ -834,26 +838,22 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Industrial Production MoMJAN</t>
+          <t>Manufacturing Production YoYJAN</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>0.5%</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+          <t>1%</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.8%</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="16">
@@ -1746,18 +1746,22 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Housing Starts MoMJAN</t>
+          <t>Building Permits PrelJAN</t>
         </is>
       </c>
       <c r="C61" t="inlineStr"/>
-      <c r="D61" t="inlineStr"/>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>1.45M</t>
+        </is>
+      </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>-9.0%</t>
+          <t>1.47M</t>
         </is>
       </c>
       <c r="F61" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="62">
@@ -1794,14 +1798,14 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Building Permits MoM PrelJAN</t>
+          <t>Housing Starts MoMJAN</t>
         </is>
       </c>
       <c r="C63" t="inlineStr"/>
       <c r="D63" t="inlineStr"/>
       <c r="E63" t="inlineStr">
         <is>
-          <t>-0.8%</t>
+          <t>-9.0%</t>
         </is>
       </c>
       <c r="F63" t="n">
@@ -1842,22 +1846,18 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Building Permits PrelJAN</t>
+          <t>Building Permits MoM PrelJAN</t>
         </is>
       </c>
       <c r="C65" t="inlineStr"/>
-      <c r="D65" t="inlineStr">
-        <is>
-          <t>1.45M</t>
-        </is>
-      </c>
+      <c r="D65" t="inlineStr"/>
       <c r="E65" t="inlineStr">
         <is>
-          <t>1.47M</t>
+          <t>-0.8%</t>
         </is>
       </c>
       <c r="F65" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="66">
@@ -2920,14 +2920,14 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeFEB/14</t>
+          <t>15-Year Mortgage RateFEB/20</t>
         </is>
       </c>
       <c r="C120" t="inlineStr"/>
       <c r="D120" t="inlineStr"/>
       <c r="E120" t="inlineStr"/>
       <c r="F120" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="121">
@@ -2938,14 +2938,14 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeFEB/14</t>
+          <t>EIA Distillate Fuel Production ChangeFEB/14</t>
         </is>
       </c>
       <c r="C121" t="inlineStr"/>
       <c r="D121" t="inlineStr"/>
       <c r="E121" t="inlineStr"/>
       <c r="F121" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="122">
@@ -2974,14 +2974,14 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeFEB/14</t>
+          <t>EIA Gasoline Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C123" t="inlineStr"/>
       <c r="D123" t="inlineStr"/>
       <c r="E123" t="inlineStr"/>
       <c r="F123" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="124">
@@ -2992,14 +2992,14 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>15-Year Mortgage RateFEB/20</t>
+          <t>EIA Crude Oil Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C124" t="inlineStr"/>
       <c r="D124" t="inlineStr"/>
       <c r="E124" t="inlineStr"/>
       <c r="F124" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="125">
@@ -3364,7 +3364,7 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>S&amp;P Global Composite PMI FlashFEB</t>
+          <t>S&amp;P Global Services PMI FlashFEB</t>
         </is>
       </c>
       <c r="C144" t="inlineStr"/>
@@ -3408,7 +3408,7 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>S&amp;P Global Services PMI FlashFEB</t>
+          <t>S&amp;P Global Composite PMI FlashFEB</t>
         </is>
       </c>
       <c r="C146" t="inlineStr"/>
@@ -3634,22 +3634,22 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>Michigan Consumer Sentiment FinalFEB</t>
+          <t>Michigan Current Conditions FinalFEB</t>
         </is>
       </c>
       <c r="C155" t="inlineStr"/>
       <c r="D155" t="inlineStr">
         <is>
-          <t>67.8</t>
+          <t>68.7</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>67.8</t>
+          <t>68.7</t>
         </is>
       </c>
       <c r="F155" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="156">
@@ -3686,22 +3686,22 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>Michigan Current Conditions FinalFEB</t>
+          <t>Michigan Consumer Sentiment FinalFEB</t>
         </is>
       </c>
       <c r="C157" t="inlineStr"/>
       <c r="D157" t="inlineStr">
         <is>
-          <t>68.7</t>
+          <t>67.8</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>68.7</t>
+          <t>67.8</t>
         </is>
       </c>
       <c r="F157" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="158">

--- a/Input_data/EST_US_trad_eco_cal_2025-02-14_to_2025-02-25.xlsx
+++ b/Input_data/EST_US_trad_eco_cal_2025-02-14_to_2025-02-25.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F198"/>
+  <dimension ref="A1:F200"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -722,22 +722,22 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Manufacturing Production MoMJAN</t>
+          <t>Capacity UtilizationJAN</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-0.1%</t>
+          <t>77.8%</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>77.7%</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>77.4%</t>
         </is>
       </c>
       <c r="F11" t="n">
@@ -752,26 +752,22 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Industrial Production MoMJAN</t>
+          <t>Industrial Production YoYJAN</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>0.5%</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+          <t>2%</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.9%</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="13">
@@ -782,18 +778,22 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Manufacturing Production YoYJAN</t>
+          <t>Manufacturing Production MoMJAN</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>1%</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr"/>
+          <t>-0.1%</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>0.1%</t>
+        </is>
+      </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>0.8%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F13" t="n">
@@ -808,22 +808,26 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Industrial Production YoYJAN</t>
+          <t>Industrial Production MoMJAN</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>2%</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr"/>
+          <t>0.5%</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>0.9%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="15">
@@ -834,22 +838,18 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Capacity UtilizationJAN</t>
+          <t>Manufacturing Production YoYJAN</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>77.8%</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>77.7%</t>
-        </is>
-      </c>
+          <t>1%</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
-          <t>77.4%</t>
+          <t>0.8%</t>
         </is>
       </c>
       <c r="F15" t="n">
@@ -924,12 +924,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Baker Hughes Oil Rig CountFEB/14</t>
+          <t>Baker Hughes Total Rigs CountFEB/14</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>481</t>
+          <t>588</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -946,12 +946,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Baker Hughes Total Rigs CountFEB/14</t>
+          <t>Baker Hughes Oil Rig CountFEB/14</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>588</t>
+          <t>481</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -1270,7 +1270,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>6-Month Bill Auction</t>
+          <t>3-Month Bill Auction</t>
         </is>
       </c>
       <c r="C35" t="inlineStr"/>
@@ -1288,7 +1288,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>3-Month Bill Auction</t>
+          <t>6-Month Bill Auction</t>
         </is>
       </c>
       <c r="C36" t="inlineStr"/>
@@ -1342,14 +1342,14 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Fed Barr Speech</t>
+          <t>52-Week Bill Auction</t>
         </is>
       </c>
       <c r="C39" t="inlineStr"/>
       <c r="D39" t="inlineStr"/>
       <c r="E39" t="inlineStr"/>
       <c r="F39" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="40">
@@ -1396,14 +1396,14 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>52-Week Bill Auction</t>
+          <t>Fed Barr Speech</t>
         </is>
       </c>
       <c r="C42" t="inlineStr"/>
       <c r="D42" t="inlineStr"/>
       <c r="E42" t="inlineStr"/>
       <c r="F42" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="43">
@@ -1414,14 +1414,14 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Net Long-term TIC FlowsDEC</t>
+          <t>Overall Net Capital FlowsDEC</t>
         </is>
       </c>
       <c r="C43" t="inlineStr"/>
       <c r="D43" t="inlineStr"/>
       <c r="E43" t="inlineStr"/>
       <c r="F43" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="44">
@@ -1450,14 +1450,14 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Net Long-term TIC FlowsDEC</t>
+          <t>Overall Net Capital FlowsDEC</t>
         </is>
       </c>
       <c r="C45" t="inlineStr"/>
       <c r="D45" t="inlineStr"/>
       <c r="E45" t="inlineStr"/>
       <c r="F45" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="46">
@@ -1468,14 +1468,14 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Overall Net Capital FlowsDEC</t>
+          <t>Net Long-term TIC FlowsDEC</t>
         </is>
       </c>
       <c r="C46" t="inlineStr"/>
       <c r="D46" t="inlineStr"/>
       <c r="E46" t="inlineStr"/>
       <c r="F46" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="47">
@@ -1486,14 +1486,14 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Overall Net Capital FlowsDEC</t>
+          <t>Net Long-term TIC FlowsDEC</t>
         </is>
       </c>
       <c r="C47" t="inlineStr"/>
       <c r="D47" t="inlineStr"/>
       <c r="E47" t="inlineStr"/>
       <c r="F47" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="48">
@@ -1540,14 +1540,14 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>MBA 30-Year Mortgage RateFEB/14</t>
+          <t>MBA Mortgage Refinance IndexFEB/14</t>
         </is>
       </c>
       <c r="C50" t="inlineStr"/>
       <c r="D50" t="inlineStr"/>
       <c r="E50" t="inlineStr"/>
       <c r="F50" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="51">
@@ -1558,7 +1558,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>MBA Mortgage ApplicationsFEB/14</t>
+          <t>MBA Mortgage Market IndexFEB/14</t>
         </is>
       </c>
       <c r="C51" t="inlineStr"/>
@@ -1576,14 +1576,14 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>MBA 30-Year Mortgage RateFEB/14</t>
+          <t>MBA Mortgage ApplicationsFEB/14</t>
         </is>
       </c>
       <c r="C52" t="inlineStr"/>
       <c r="D52" t="inlineStr"/>
       <c r="E52" t="inlineStr"/>
       <c r="F52" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="53">
@@ -1594,14 +1594,14 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>MBA Mortgage Refinance IndexFEB/14</t>
+          <t>MBA 30-Year Mortgage RateFEB/14</t>
         </is>
       </c>
       <c r="C53" t="inlineStr"/>
       <c r="D53" t="inlineStr"/>
       <c r="E53" t="inlineStr"/>
       <c r="F53" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="54">
@@ -1612,14 +1612,14 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>MBA Mortgage Market IndexFEB/14</t>
+          <t>MBA 30-Year Mortgage RateFEB/14</t>
         </is>
       </c>
       <c r="C54" t="inlineStr"/>
       <c r="D54" t="inlineStr"/>
       <c r="E54" t="inlineStr"/>
       <c r="F54" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="55">
@@ -1648,7 +1648,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>MBA Mortgage Market IndexFEB/14</t>
+          <t>MBA Purchase IndexFEB/14</t>
         </is>
       </c>
       <c r="C56" t="inlineStr"/>
@@ -1684,7 +1684,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>MBA Purchase IndexFEB/14</t>
+          <t>MBA Mortgage Market IndexFEB/14</t>
         </is>
       </c>
       <c r="C58" t="inlineStr"/>
@@ -1702,22 +1702,18 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Building Permits PrelJAN</t>
+          <t>Housing Starts MoMJAN</t>
         </is>
       </c>
       <c r="C59" t="inlineStr"/>
-      <c r="D59" t="inlineStr">
-        <is>
-          <t>1.45M</t>
-        </is>
-      </c>
+      <c r="D59" t="inlineStr"/>
       <c r="E59" t="inlineStr">
         <is>
-          <t>1.47M</t>
+          <t>-9.0%</t>
         </is>
       </c>
       <c r="F59" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="60">
@@ -1728,18 +1724,22 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Housing Starts MoMJAN</t>
+          <t>Housing StartsJAN</t>
         </is>
       </c>
       <c r="C60" t="inlineStr"/>
-      <c r="D60" t="inlineStr"/>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>1.39M</t>
+        </is>
+      </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>-9.0%</t>
+          <t>1.35M</t>
         </is>
       </c>
       <c r="F60" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="61">
@@ -1772,14 +1772,14 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Housing Starts MoMJAN</t>
+          <t>Building Permits MoM PrelJAN</t>
         </is>
       </c>
       <c r="C62" t="inlineStr"/>
       <c r="D62" t="inlineStr"/>
       <c r="E62" t="inlineStr">
         <is>
-          <t>-9.0%</t>
+          <t>-0.8%</t>
         </is>
       </c>
       <c r="F62" t="n">
@@ -1794,14 +1794,14 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Building Permits MoM PrelJAN</t>
+          <t>Housing Starts MoMJAN</t>
         </is>
       </c>
       <c r="C63" t="inlineStr"/>
       <c r="D63" t="inlineStr"/>
       <c r="E63" t="inlineStr">
         <is>
-          <t>-0.8%</t>
+          <t>-9.0%</t>
         </is>
       </c>
       <c r="F63" t="n">
@@ -1868,18 +1868,18 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Housing StartsJAN</t>
+          <t>Building Permits PrelJAN</t>
         </is>
       </c>
       <c r="C66" t="inlineStr"/>
       <c r="D66" t="inlineStr">
         <is>
-          <t>1.39M</t>
+          <t>1.45M</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>1.35M</t>
+          <t>1.47M</t>
         </is>
       </c>
       <c r="F66" t="n">
@@ -2154,7 +2154,7 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Philly Fed New OrdersFEB</t>
+          <t>Philly Fed Prices PaidFEB</t>
         </is>
       </c>
       <c r="C81" t="inlineStr"/>
@@ -2172,16 +2172,12 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsFEB/08</t>
+          <t>Philly Fed CAPEX IndexFEB</t>
         </is>
       </c>
       <c r="C82" t="inlineStr"/>
       <c r="D82" t="inlineStr"/>
-      <c r="E82" t="inlineStr">
-        <is>
-          <t>1879.0K</t>
-        </is>
-      </c>
+      <c r="E82" t="inlineStr"/>
       <c r="F82" t="n">
         <v>3</v>
       </c>
@@ -2194,16 +2190,12 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageFEB/15</t>
+          <t>Philly Fed Business ConditionsFEB</t>
         </is>
       </c>
       <c r="C83" t="inlineStr"/>
       <c r="D83" t="inlineStr"/>
-      <c r="E83" t="inlineStr">
-        <is>
-          <t>219.0K</t>
-        </is>
-      </c>
+      <c r="E83" t="inlineStr"/>
       <c r="F83" t="n">
         <v>3</v>
       </c>
@@ -2216,12 +2208,16 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Philly Fed Business ConditionsFEB</t>
+          <t>Jobless Claims 4-week AverageFEB/15</t>
         </is>
       </c>
       <c r="C84" t="inlineStr"/>
       <c r="D84" t="inlineStr"/>
-      <c r="E84" t="inlineStr"/>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>219.0K</t>
+        </is>
+      </c>
       <c r="F84" t="n">
         <v>3</v>
       </c>
@@ -2234,12 +2230,16 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Philly Fed CAPEX IndexFEB</t>
+          <t>Continuing Jobless ClaimsFEB/08</t>
         </is>
       </c>
       <c r="C85" t="inlineStr"/>
       <c r="D85" t="inlineStr"/>
-      <c r="E85" t="inlineStr"/>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>1879.0K</t>
+        </is>
+      </c>
       <c r="F85" t="n">
         <v>3</v>
       </c>
@@ -2252,14 +2252,22 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Philly Fed EmploymentFEB</t>
+          <t>Philadelphia Fed Manufacturing IndexFEB</t>
         </is>
       </c>
       <c r="C86" t="inlineStr"/>
-      <c r="D86" t="inlineStr"/>
-      <c r="E86" t="inlineStr"/>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>25.5</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
       <c r="F86" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="87">
@@ -2270,14 +2278,22 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Philly Fed Prices PaidFEB</t>
+          <t>Initial Jobless ClaimsFEB/15</t>
         </is>
       </c>
       <c r="C87" t="inlineStr"/>
-      <c r="D87" t="inlineStr"/>
-      <c r="E87" t="inlineStr"/>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>216K</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>220.0K</t>
+        </is>
+      </c>
       <c r="F87" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="88">
@@ -2288,22 +2304,14 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Philadelphia Fed Manufacturing IndexFEB</t>
+          <t>Philly Fed New OrdersFEB</t>
         </is>
       </c>
       <c r="C88" t="inlineStr"/>
-      <c r="D88" t="inlineStr">
-        <is>
-          <t>25.5</t>
-        </is>
-      </c>
-      <c r="E88" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
+      <c r="D88" t="inlineStr"/>
+      <c r="E88" t="inlineStr"/>
       <c r="F88" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="89">
@@ -2314,16 +2322,12 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsFEB/08</t>
+          <t>Philly Fed EmploymentFEB</t>
         </is>
       </c>
       <c r="C89" t="inlineStr"/>
       <c r="D89" t="inlineStr"/>
-      <c r="E89" t="inlineStr">
-        <is>
-          <t>1879.0K</t>
-        </is>
-      </c>
+      <c r="E89" t="inlineStr"/>
       <c r="F89" t="n">
         <v>3</v>
       </c>
@@ -2336,18 +2340,18 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Philadelphia Fed Manufacturing IndexFEB</t>
+          <t>Initial Jobless ClaimsFEB/15</t>
         </is>
       </c>
       <c r="C90" t="inlineStr"/>
       <c r="D90" t="inlineStr">
         <is>
-          <t>25.5</t>
+          <t>216K</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>220.0K</t>
         </is>
       </c>
       <c r="F90" t="n">
@@ -2362,16 +2366,12 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageFEB/15</t>
+          <t>Philly Fed New OrdersFEB</t>
         </is>
       </c>
       <c r="C91" t="inlineStr"/>
       <c r="D91" t="inlineStr"/>
-      <c r="E91" t="inlineStr">
-        <is>
-          <t>219.0K</t>
-        </is>
-      </c>
+      <c r="E91" t="inlineStr"/>
       <c r="F91" t="n">
         <v>3</v>
       </c>
@@ -2384,7 +2384,7 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Philly Fed Business ConditionsFEB</t>
+          <t>Philly Fed CAPEX IndexFEB</t>
         </is>
       </c>
       <c r="C92" t="inlineStr"/>
@@ -2402,7 +2402,7 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Philly Fed CAPEX IndexFEB</t>
+          <t>Philly Fed Business ConditionsFEB</t>
         </is>
       </c>
       <c r="C93" t="inlineStr"/>
@@ -2420,22 +2420,18 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsFEB/15</t>
+          <t>Jobless Claims 4-week AverageFEB/15</t>
         </is>
       </c>
       <c r="C94" t="inlineStr"/>
-      <c r="D94" t="inlineStr">
-        <is>
-          <t>216K</t>
-        </is>
-      </c>
+      <c r="D94" t="inlineStr"/>
       <c r="E94" t="inlineStr">
         <is>
-          <t>220.0K</t>
+          <t>219.0K</t>
         </is>
       </c>
       <c r="F94" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="95">
@@ -2446,14 +2442,22 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Philly Fed New OrdersFEB</t>
+          <t>Philadelphia Fed Manufacturing IndexFEB</t>
         </is>
       </c>
       <c r="C95" t="inlineStr"/>
-      <c r="D95" t="inlineStr"/>
-      <c r="E95" t="inlineStr"/>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>25.5</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
       <c r="F95" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="96">
@@ -2464,22 +2468,18 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsFEB/15</t>
+          <t>Continuing Jobless ClaimsFEB/08</t>
         </is>
       </c>
       <c r="C96" t="inlineStr"/>
-      <c r="D96" t="inlineStr">
-        <is>
-          <t>216K</t>
-        </is>
-      </c>
+      <c r="D96" t="inlineStr"/>
       <c r="E96" t="inlineStr">
         <is>
-          <t>220.0K</t>
+          <t>1879.0K</t>
         </is>
       </c>
       <c r="F96" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="97">
@@ -2650,7 +2650,7 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>8-Week Bill Auction</t>
+          <t>4-Week Bill Auction</t>
         </is>
       </c>
       <c r="C105" t="inlineStr"/>
@@ -2668,7 +2668,7 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>4-Week Bill Auction</t>
+          <t>8-Week Bill Auction</t>
         </is>
       </c>
       <c r="C106" t="inlineStr"/>
@@ -2722,14 +2722,14 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeFEB/14</t>
+          <t>EIA Distillate Fuel Production ChangeFEB/14</t>
         </is>
       </c>
       <c r="C109" t="inlineStr"/>
       <c r="D109" t="inlineStr"/>
       <c r="E109" t="inlineStr"/>
       <c r="F109" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="110">
@@ -2740,7 +2740,7 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeFEB/14</t>
+          <t>EIA Crude Oil Imports ChangeFEB/14</t>
         </is>
       </c>
       <c r="C110" t="inlineStr"/>
@@ -2758,7 +2758,7 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeFEB/14</t>
+          <t>30-Year Mortgage RateFEB/20</t>
         </is>
       </c>
       <c r="C111" t="inlineStr"/>
@@ -2776,14 +2776,14 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeFEB/14</t>
+          <t>EIA Crude Oil Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C112" t="inlineStr"/>
       <c r="D112" t="inlineStr"/>
       <c r="E112" t="inlineStr"/>
       <c r="F112" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="113">
@@ -2812,7 +2812,7 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeFEB/14</t>
+          <t>EIA Gasoline Production ChangeFEB/14</t>
         </is>
       </c>
       <c r="C114" t="inlineStr"/>
@@ -2830,7 +2830,7 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeFEB/14</t>
+          <t>EIA Heating Oil Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C115" t="inlineStr"/>
@@ -2848,14 +2848,14 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeFEB/14</t>
+          <t>EIA Gasoline Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C116" t="inlineStr"/>
       <c r="D116" t="inlineStr"/>
       <c r="E116" t="inlineStr"/>
       <c r="F116" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="117">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>30-Year Mortgage RateFEB/20</t>
+          <t>EIA Refinery Crude Runs ChangeFEB/14</t>
         </is>
       </c>
       <c r="C117" t="inlineStr"/>
@@ -2884,7 +2884,7 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeFEB/14</t>
+          <t>EIA Heating Oil Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C118" t="inlineStr"/>
@@ -2902,7 +2902,7 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeFEB/14</t>
+          <t>EIA Gasoline Production ChangeFEB/14</t>
         </is>
       </c>
       <c r="C119" t="inlineStr"/>
@@ -2920,7 +2920,7 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>30-Year Mortgage RateFEB/20</t>
+          <t>EIA Distillate Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C120" t="inlineStr"/>
@@ -2938,7 +2938,7 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>15-Year Mortgage RateFEB/20</t>
+          <t>EIA Distillate Fuel Production ChangeFEB/14</t>
         </is>
       </c>
       <c r="C121" t="inlineStr"/>
@@ -2956,14 +2956,14 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeFEB/14</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C122" t="inlineStr"/>
       <c r="D122" t="inlineStr"/>
       <c r="E122" t="inlineStr"/>
       <c r="F122" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="123">
@@ -2974,14 +2974,14 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeFEB/14</t>
+          <t>EIA Crude Oil Imports ChangeFEB/14</t>
         </is>
       </c>
       <c r="C123" t="inlineStr"/>
       <c r="D123" t="inlineStr"/>
       <c r="E123" t="inlineStr"/>
       <c r="F123" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="124">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeFEB/14</t>
+          <t>EIA Refinery Crude Runs ChangeFEB/14</t>
         </is>
       </c>
       <c r="C124" t="inlineStr"/>
@@ -3010,7 +3010,7 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeFEB/14</t>
+          <t>15-Year Mortgage RateFEB/20</t>
         </is>
       </c>
       <c r="C125" t="inlineStr"/>
@@ -3028,7 +3028,7 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeFEB/14</t>
+          <t>30-Year Mortgage RateFEB/20</t>
         </is>
       </c>
       <c r="C126" t="inlineStr"/>
@@ -3046,14 +3046,14 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeFEB/14</t>
+          <t>EIA Crude Oil Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C127" t="inlineStr"/>
       <c r="D127" t="inlineStr"/>
       <c r="E127" t="inlineStr"/>
       <c r="F127" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="128">
@@ -3064,14 +3064,14 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeFEB/14</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C128" t="inlineStr"/>
       <c r="D128" t="inlineStr"/>
       <c r="E128" t="inlineStr"/>
       <c r="F128" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="129">
@@ -3100,14 +3100,14 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeFEB/14</t>
+          <t>EIA Gasoline Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C130" t="inlineStr"/>
       <c r="D130" t="inlineStr"/>
       <c r="E130" t="inlineStr"/>
       <c r="F130" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="131">
@@ -3298,7 +3298,7 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>S&amp;P Global Composite PMI FlashFEB</t>
+          <t>S&amp;P Global Services PMI FlashFEB</t>
         </is>
       </c>
       <c r="C141" t="inlineStr"/>
@@ -3320,7 +3320,7 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>S&amp;P Global Services PMI FlashFEB</t>
+          <t>S&amp;P Global Composite PMI FlashFEB</t>
         </is>
       </c>
       <c r="C142" t="inlineStr"/>
@@ -3364,7 +3364,7 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>S&amp;P Global Composite PMI FlashFEB</t>
+          <t>S&amp;P Global Services PMI FlashFEB</t>
         </is>
       </c>
       <c r="C144" t="inlineStr"/>
@@ -3386,7 +3386,7 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>S&amp;P Global Services PMI FlashFEB</t>
+          <t>S&amp;P Global Composite PMI FlashFEB</t>
         </is>
       </c>
       <c r="C145" t="inlineStr"/>
@@ -3430,22 +3430,22 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Michigan Consumer Expectations FinalFEB</t>
+          <t>Existing Home SalesJAN</t>
         </is>
       </c>
       <c r="C147" t="inlineStr"/>
       <c r="D147" t="inlineStr">
         <is>
-          <t>67.3</t>
+          <t>4.17M</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>67.3</t>
+          <t>4.16M</t>
         </is>
       </c>
       <c r="F147" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="148">
@@ -3456,22 +3456,22 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Existing Home SalesJAN</t>
+          <t>Michigan Inflation Expectations FinalFEB</t>
         </is>
       </c>
       <c r="C148" t="inlineStr"/>
       <c r="D148" t="inlineStr">
         <is>
-          <t>4.17M</t>
+          <t>4.3%</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>4.16M</t>
+          <t>4.3%</t>
         </is>
       </c>
       <c r="F148" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="149">
@@ -3504,22 +3504,22 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Michigan Consumer Sentiment FinalFEB</t>
+          <t>Michigan Consumer Expectations FinalFEB</t>
         </is>
       </c>
       <c r="C150" t="inlineStr"/>
       <c r="D150" t="inlineStr">
         <is>
-          <t>67.8</t>
+          <t>67.3</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>67.8</t>
+          <t>67.3</t>
         </is>
       </c>
       <c r="F150" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="151">
@@ -3530,18 +3530,18 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Michigan Inflation Expectations FinalFEB</t>
+          <t>Michigan 5 Year Inflation Expectations FinalFEB</t>
         </is>
       </c>
       <c r="C151" t="inlineStr"/>
       <c r="D151" t="inlineStr">
         <is>
-          <t>4.3%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>4.3%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="F151" t="n">
@@ -3556,22 +3556,22 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Michigan Current Conditions FinalFEB</t>
+          <t>Michigan Consumer Sentiment FinalFEB</t>
         </is>
       </c>
       <c r="C152" t="inlineStr"/>
       <c r="D152" t="inlineStr">
         <is>
-          <t>68.7</t>
+          <t>67.8</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>68.7</t>
+          <t>67.8</t>
         </is>
       </c>
       <c r="F152" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="153">
@@ -3582,18 +3582,18 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>Michigan 5 Year Inflation Expectations FinalFEB</t>
+          <t>Michigan Current Conditions FinalFEB</t>
         </is>
       </c>
       <c r="C153" t="inlineStr"/>
       <c r="D153" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>68.7</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>68.7</t>
         </is>
       </c>
       <c r="F153" t="n">
@@ -3608,22 +3608,22 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>Existing Home SalesJAN</t>
+          <t>Michigan Inflation Expectations FinalFEB</t>
         </is>
       </c>
       <c r="C154" t="inlineStr"/>
       <c r="D154" t="inlineStr">
         <is>
-          <t>4.17M</t>
+          <t>4.3%</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>4.16M</t>
+          <t>4.3%</t>
         </is>
       </c>
       <c r="F154" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="155">
@@ -3634,18 +3634,18 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>Michigan Inflation Expectations FinalFEB</t>
+          <t>Michigan Current Conditions FinalFEB</t>
         </is>
       </c>
       <c r="C155" t="inlineStr"/>
       <c r="D155" t="inlineStr">
         <is>
-          <t>4.3%</t>
+          <t>68.7</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>4.3%</t>
+          <t>68.7</t>
         </is>
       </c>
       <c r="F155" t="n">
@@ -3660,18 +3660,22 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>Existing Home Sales MoMJAN</t>
+          <t>Michigan Consumer Expectations FinalFEB</t>
         </is>
       </c>
       <c r="C156" t="inlineStr"/>
-      <c r="D156" t="inlineStr"/>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>67.3</t>
+        </is>
+      </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>-1.7%</t>
+          <t>67.3</t>
         </is>
       </c>
       <c r="F156" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="157">
@@ -3682,18 +3686,18 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>Michigan Current Conditions FinalFEB</t>
+          <t>Michigan 5 Year Inflation Expectations FinalFEB</t>
         </is>
       </c>
       <c r="C157" t="inlineStr"/>
       <c r="D157" t="inlineStr">
         <is>
-          <t>68.7</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>68.7</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="F157" t="n">
@@ -3708,22 +3712,22 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>Michigan Consumer Expectations FinalFEB</t>
+          <t>Michigan Consumer Sentiment FinalFEB</t>
         </is>
       </c>
       <c r="C158" t="inlineStr"/>
       <c r="D158" t="inlineStr">
         <is>
-          <t>67.3</t>
+          <t>67.8</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>67.3</t>
+          <t>67.8</t>
         </is>
       </c>
       <c r="F158" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="159">
@@ -3734,22 +3738,18 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>Michigan 5 Year Inflation Expectations FinalFEB</t>
+          <t>Existing Home Sales MoMJAN</t>
         </is>
       </c>
       <c r="C159" t="inlineStr"/>
-      <c r="D159" t="inlineStr">
-        <is>
-          <t>3.3%</t>
-        </is>
-      </c>
+      <c r="D159" t="inlineStr"/>
       <c r="E159" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>-1.7%</t>
         </is>
       </c>
       <c r="F159" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="160">
@@ -3760,22 +3760,22 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>Michigan Consumer Sentiment FinalFEB</t>
+          <t>Existing Home SalesJAN</t>
         </is>
       </c>
       <c r="C160" t="inlineStr"/>
       <c r="D160" t="inlineStr">
         <is>
-          <t>67.8</t>
+          <t>4.17M</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>67.8</t>
+          <t>4.16M</t>
         </is>
       </c>
       <c r="F160" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="161">
@@ -3858,7 +3858,7 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>Baker Hughes Total Rigs CountFEB/21</t>
+          <t>Baker Hughes Oil Rig CountFEB/21</t>
         </is>
       </c>
       <c r="C165" t="inlineStr"/>
@@ -3876,7 +3876,7 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>Baker Hughes Oil Rig CountFEB/21</t>
+          <t>Baker Hughes Total Rigs CountFEB/21</t>
         </is>
       </c>
       <c r="C166" t="inlineStr"/>
@@ -3966,7 +3966,7 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>6-Month Bill Auction</t>
+          <t>3-Month Bill Auction</t>
         </is>
       </c>
       <c r="C171" t="inlineStr"/>
@@ -4020,7 +4020,7 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>3-Month Bill Auction</t>
+          <t>6-Month Bill Auction</t>
         </is>
       </c>
       <c r="C174" t="inlineStr"/>
@@ -4204,7 +4204,7 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>House Price IndexDEC</t>
+          <t>House Price Index YoYDEC</t>
         </is>
       </c>
       <c r="C184" t="inlineStr"/>
@@ -4222,18 +4222,14 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>S&amp;P/Case-Shiller Home Price YoYDEC</t>
+          <t>House Price Index MoMDEC</t>
         </is>
       </c>
       <c r="C185" t="inlineStr"/>
       <c r="D185" t="inlineStr"/>
-      <c r="E185" t="inlineStr">
-        <is>
-          <t>4.2%</t>
-        </is>
-      </c>
+      <c r="E185" t="inlineStr"/>
       <c r="F185" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="186">
@@ -4244,7 +4240,7 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>House Price Index MoMDEC</t>
+          <t>S&amp;P/Case-Shiller Home Price MoMDEC</t>
         </is>
       </c>
       <c r="C186" t="inlineStr"/>
@@ -4262,14 +4258,18 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>S&amp;P/Case-Shiller Home Price MoMDEC</t>
+          <t>S&amp;P/Case-Shiller Home Price YoYDEC</t>
         </is>
       </c>
       <c r="C187" t="inlineStr"/>
       <c r="D187" t="inlineStr"/>
-      <c r="E187" t="inlineStr"/>
+      <c r="E187" t="inlineStr">
+        <is>
+          <t>4.2%</t>
+        </is>
+      </c>
       <c r="F187" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="188">
@@ -4280,7 +4280,7 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>House Price Index YoYDEC</t>
+          <t>House Price IndexDEC</t>
         </is>
       </c>
       <c r="C188" t="inlineStr"/>
@@ -4298,7 +4298,7 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>Richmond Fed Manufacturing IndexFEB</t>
+          <t>Richmond Fed Services Revenues IndexFEB</t>
         </is>
       </c>
       <c r="C189" t="inlineStr"/>
@@ -4316,14 +4316,14 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>CB Consumer ConfidenceFEB</t>
+          <t>Richmond Fed Manufacturing Shipments IndexFEB</t>
         </is>
       </c>
       <c r="C190" t="inlineStr"/>
       <c r="D190" t="inlineStr"/>
       <c r="E190" t="inlineStr"/>
       <c r="F190" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="191">
@@ -4334,7 +4334,7 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>Richmond Fed Manufacturing Shipments IndexFEB</t>
+          <t>Richmond Fed Manufacturing IndexFEB</t>
         </is>
       </c>
       <c r="C191" t="inlineStr"/>
@@ -4352,14 +4352,14 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>CB Consumer ConfidenceFEB</t>
+          <t>Richmond Fed Services Revenues IndexFEB</t>
         </is>
       </c>
       <c r="C192" t="inlineStr"/>
       <c r="D192" t="inlineStr"/>
       <c r="E192" t="inlineStr"/>
       <c r="F192" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="193">
@@ -4370,14 +4370,14 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>Richmond Fed Manufacturing IndexFEB</t>
+          <t>CB Consumer ConfidenceFEB</t>
         </is>
       </c>
       <c r="C193" t="inlineStr"/>
       <c r="D193" t="inlineStr"/>
       <c r="E193" t="inlineStr"/>
       <c r="F193" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="194">
@@ -4406,7 +4406,7 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>Richmond Fed Services Revenues IndexFEB</t>
+          <t>Richmond Fed Manufacturing IndexFEB</t>
         </is>
       </c>
       <c r="C195" t="inlineStr"/>
@@ -4424,14 +4424,14 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>Richmond Fed Services Revenues IndexFEB</t>
+          <t>CB Consumer ConfidenceFEB</t>
         </is>
       </c>
       <c r="C196" t="inlineStr"/>
       <c r="D196" t="inlineStr"/>
       <c r="E196" t="inlineStr"/>
       <c r="F196" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="197">
@@ -4460,7 +4460,7 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>Dallas Fed Services Revenues IndexFEB</t>
+          <t>Dallas Fed Services IndexFEB</t>
         </is>
       </c>
       <c r="C198" t="inlineStr"/>
@@ -4470,6 +4470,42 @@
         <v>3</v>
       </c>
     </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>2025-02-25 10:30:00-05:00</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>Dallas Fed Services Revenues IndexFEB</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr"/>
+      <c r="D199" t="inlineStr"/>
+      <c r="E199" t="inlineStr"/>
+      <c r="F199" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>2025-02-25 10:30:00-05:00</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>Dallas Fed Services Revenues IndexFEB</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr"/>
+      <c r="D200" t="inlineStr"/>
+      <c r="E200" t="inlineStr"/>
+      <c r="F200" t="n">
+        <v>3</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Input_data/EST_US_trad_eco_cal_2025-02-14_to_2025-02-25.xlsx
+++ b/Input_data/EST_US_trad_eco_cal_2025-02-14_to_2025-02-25.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F202"/>
+  <dimension ref="A1:F204"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -864,26 +864,26 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Retail Inventories Ex Autos MoMDEC</t>
+          <t>Business Inventories MoMDEC</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
+          <t>-0.2%</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
           <t>-0.1%</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>0.2%</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>0.2%</t>
-        </is>
-      </c>
       <c r="F16" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="17">
@@ -894,26 +894,26 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Business Inventories MoMDEC</t>
+          <t>Retail Inventories Ex Autos MoMDEC</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>-0.2%</t>
+          <t>-0.1%</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>-0.1%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="18">
@@ -1378,14 +1378,14 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>52-Week Bill Auction</t>
+          <t>Fed Barr Speech</t>
         </is>
       </c>
       <c r="C41" t="inlineStr"/>
       <c r="D41" t="inlineStr"/>
       <c r="E41" t="inlineStr"/>
       <c r="F41" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="42">
@@ -1396,14 +1396,14 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Fed Barr Speech</t>
+          <t>52-Week Bill Auction</t>
         </is>
       </c>
       <c r="C42" t="inlineStr"/>
       <c r="D42" t="inlineStr"/>
       <c r="E42" t="inlineStr"/>
       <c r="F42" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="43">
@@ -1414,14 +1414,14 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Net Long-term TIC FlowsDEC</t>
+          <t>Foreign Bond InvestmentDEC</t>
         </is>
       </c>
       <c r="C43" t="inlineStr"/>
       <c r="D43" t="inlineStr"/>
       <c r="E43" t="inlineStr"/>
       <c r="F43" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="44">
@@ -1432,14 +1432,18 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Foreign Bond InvestmentDEC</t>
+          <t>Net Long-term TIC FlowsDEC</t>
         </is>
       </c>
       <c r="C44" t="inlineStr"/>
-      <c r="D44" t="inlineStr"/>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>$149.1B</t>
+        </is>
+      </c>
       <c r="E44" t="inlineStr"/>
       <c r="F44" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="45">
@@ -1468,14 +1472,14 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Net Long-term TIC FlowsDEC</t>
+          <t>Foreign Bond InvestmentDEC</t>
         </is>
       </c>
       <c r="C46" t="inlineStr"/>
       <c r="D46" t="inlineStr"/>
       <c r="E46" t="inlineStr"/>
       <c r="F46" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="47">
@@ -1486,14 +1490,14 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Foreign Bond InvestmentDEC</t>
+          <t>Net Long-term TIC FlowsDEC</t>
         </is>
       </c>
       <c r="C47" t="inlineStr"/>
       <c r="D47" t="inlineStr"/>
       <c r="E47" t="inlineStr"/>
       <c r="F47" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="48">
@@ -1522,14 +1526,14 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>MBA 30-Year Mortgage RateFEB/14</t>
+          <t>MBA Purchase IndexFEB/14</t>
         </is>
       </c>
       <c r="C49" t="inlineStr"/>
       <c r="D49" t="inlineStr"/>
       <c r="E49" t="inlineStr"/>
       <c r="F49" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="50">
@@ -1540,14 +1544,14 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>MBA 30-Year Mortgage RateFEB/14</t>
+          <t>MBA Mortgage Refinance IndexFEB/14</t>
         </is>
       </c>
       <c r="C50" t="inlineStr"/>
       <c r="D50" t="inlineStr"/>
       <c r="E50" t="inlineStr"/>
       <c r="F50" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="51">
@@ -1558,7 +1562,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>MBA Mortgage ApplicationsFEB/14</t>
+          <t>MBA Mortgage Market IndexFEB/14</t>
         </is>
       </c>
       <c r="C51" t="inlineStr"/>
@@ -1576,14 +1580,14 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>MBA Purchase IndexFEB/14</t>
+          <t>MBA 30-Year Mortgage RateFEB/14</t>
         </is>
       </c>
       <c r="C52" t="inlineStr"/>
       <c r="D52" t="inlineStr"/>
       <c r="E52" t="inlineStr"/>
       <c r="F52" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="53">
@@ -1594,7 +1598,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>MBA Mortgage Refinance IndexFEB/14</t>
+          <t>MBA Mortgage ApplicationsFEB/14</t>
         </is>
       </c>
       <c r="C53" t="inlineStr"/>
@@ -1630,7 +1634,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>MBA Purchase IndexFEB/14</t>
+          <t>MBA Mortgage Refinance IndexFEB/14</t>
         </is>
       </c>
       <c r="C55" t="inlineStr"/>
@@ -1648,7 +1652,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>MBA Mortgage Refinance IndexFEB/14</t>
+          <t>MBA Purchase IndexFEB/14</t>
         </is>
       </c>
       <c r="C56" t="inlineStr"/>
@@ -1666,7 +1670,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>MBA Mortgage Market IndexFEB/14</t>
+          <t>MBA Mortgage ApplicationsFEB/14</t>
         </is>
       </c>
       <c r="C57" t="inlineStr"/>
@@ -1684,14 +1688,14 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>MBA Mortgage ApplicationsFEB/14</t>
+          <t>MBA 30-Year Mortgage RateFEB/14</t>
         </is>
       </c>
       <c r="C58" t="inlineStr"/>
       <c r="D58" t="inlineStr"/>
       <c r="E58" t="inlineStr"/>
       <c r="F58" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="59">
@@ -1702,22 +1706,18 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Building Permits PrelJAN</t>
+          <t>Building Permits MoM PrelJAN</t>
         </is>
       </c>
       <c r="C59" t="inlineStr"/>
-      <c r="D59" t="inlineStr">
-        <is>
-          <t>1.45M</t>
-        </is>
-      </c>
+      <c r="D59" t="inlineStr"/>
       <c r="E59" t="inlineStr">
         <is>
-          <t>1.47M</t>
+          <t>-0.8%</t>
         </is>
       </c>
       <c r="F59" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="60">
@@ -1750,18 +1750,22 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Building Permits MoM PrelJAN</t>
+          <t>Housing StartsJAN</t>
         </is>
       </c>
       <c r="C61" t="inlineStr"/>
-      <c r="D61" t="inlineStr"/>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>1.39M</t>
+        </is>
+      </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>-0.8%</t>
+          <t>1.35M</t>
         </is>
       </c>
       <c r="F61" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="62">
@@ -1772,18 +1776,18 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Housing StartsJAN</t>
+          <t>Building Permits PrelJAN</t>
         </is>
       </c>
       <c r="C62" t="inlineStr"/>
       <c r="D62" t="inlineStr">
         <is>
-          <t>1.39M</t>
+          <t>1.45M</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>1.35M</t>
+          <t>1.47M</t>
         </is>
       </c>
       <c r="F62" t="n">
@@ -1798,22 +1802,18 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Building Permits PrelJAN</t>
+          <t>Housing Starts MoMJAN</t>
         </is>
       </c>
       <c r="C63" t="inlineStr"/>
-      <c r="D63" t="inlineStr">
-        <is>
-          <t>1.45M</t>
-        </is>
-      </c>
+      <c r="D63" t="inlineStr"/>
       <c r="E63" t="inlineStr">
         <is>
-          <t>1.47M</t>
+          <t>-9.0%</t>
         </is>
       </c>
       <c r="F63" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="64">
@@ -1824,22 +1824,18 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Housing StartsJAN</t>
+          <t>Building Permits MoM PrelJAN</t>
         </is>
       </c>
       <c r="C64" t="inlineStr"/>
-      <c r="D64" t="inlineStr">
-        <is>
-          <t>1.39M</t>
-        </is>
-      </c>
+      <c r="D64" t="inlineStr"/>
       <c r="E64" t="inlineStr">
         <is>
-          <t>1.35M</t>
+          <t>-0.8%</t>
         </is>
       </c>
       <c r="F64" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="65">
@@ -1850,18 +1846,22 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Housing Starts MoMJAN</t>
+          <t>Housing StartsJAN</t>
         </is>
       </c>
       <c r="C65" t="inlineStr"/>
-      <c r="D65" t="inlineStr"/>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>1.39M</t>
+        </is>
+      </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>-9.0%</t>
+          <t>1.35M</t>
         </is>
       </c>
       <c r="F65" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="66">
@@ -1872,18 +1872,22 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Building Permits MoM PrelJAN</t>
+          <t>Building Permits PrelJAN</t>
         </is>
       </c>
       <c r="C66" t="inlineStr"/>
-      <c r="D66" t="inlineStr"/>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>1.45M</t>
+        </is>
+      </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>-0.8%</t>
+          <t>1.47M</t>
         </is>
       </c>
       <c r="F66" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="67">
@@ -2154,18 +2158,18 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsFEB/15</t>
+          <t>Philadelphia Fed Manufacturing IndexFEB</t>
         </is>
       </c>
       <c r="C81" t="inlineStr"/>
       <c r="D81" t="inlineStr">
         <is>
-          <t>216K</t>
+          <t>25.5</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>220.0K</t>
+          <t>18</t>
         </is>
       </c>
       <c r="F81" t="n">
@@ -2180,18 +2184,22 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsFEB/08</t>
+          <t>Initial Jobless ClaimsFEB/15</t>
         </is>
       </c>
       <c r="C82" t="inlineStr"/>
-      <c r="D82" t="inlineStr"/>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>216K</t>
+        </is>
+      </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>1879.0K</t>
+          <t>220.0K</t>
         </is>
       </c>
       <c r="F82" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="83">
@@ -2202,22 +2210,14 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsFEB/15</t>
+          <t>Philly Fed New OrdersFEB</t>
         </is>
       </c>
       <c r="C83" t="inlineStr"/>
-      <c r="D83" t="inlineStr">
-        <is>
-          <t>216K</t>
-        </is>
-      </c>
-      <c r="E83" t="inlineStr">
-        <is>
-          <t>220.0K</t>
-        </is>
-      </c>
+      <c r="D83" t="inlineStr"/>
+      <c r="E83" t="inlineStr"/>
       <c r="F83" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="84">
@@ -2228,7 +2228,7 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Philly Fed New OrdersFEB</t>
+          <t>Philly Fed CAPEX IndexFEB</t>
         </is>
       </c>
       <c r="C84" t="inlineStr"/>
@@ -2246,7 +2246,7 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Philly Fed CAPEX IndexFEB</t>
+          <t>Philly Fed EmploymentFEB</t>
         </is>
       </c>
       <c r="C85" t="inlineStr"/>
@@ -2264,12 +2264,16 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Philly Fed Business ConditionsFEB</t>
+          <t>Continuing Jobless ClaimsFEB/08</t>
         </is>
       </c>
       <c r="C86" t="inlineStr"/>
       <c r="D86" t="inlineStr"/>
-      <c r="E86" t="inlineStr"/>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>1879.0K</t>
+        </is>
+      </c>
       <c r="F86" t="n">
         <v>3</v>
       </c>
@@ -2282,16 +2286,12 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageFEB/15</t>
+          <t>Philly Fed Prices PaidFEB</t>
         </is>
       </c>
       <c r="C87" t="inlineStr"/>
       <c r="D87" t="inlineStr"/>
-      <c r="E87" t="inlineStr">
-        <is>
-          <t>219.0K</t>
-        </is>
-      </c>
+      <c r="E87" t="inlineStr"/>
       <c r="F87" t="n">
         <v>3</v>
       </c>
@@ -2304,22 +2304,14 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Philadelphia Fed Manufacturing IndexFEB</t>
+          <t>Philly Fed Business ConditionsFEB</t>
         </is>
       </c>
       <c r="C88" t="inlineStr"/>
-      <c r="D88" t="inlineStr">
-        <is>
-          <t>25.5</t>
-        </is>
-      </c>
-      <c r="E88" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
+      <c r="D88" t="inlineStr"/>
+      <c r="E88" t="inlineStr"/>
       <c r="F88" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="89">
@@ -2330,14 +2322,14 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsFEB/08</t>
+          <t>Jobless Claims 4-week AverageFEB/15</t>
         </is>
       </c>
       <c r="C89" t="inlineStr"/>
       <c r="D89" t="inlineStr"/>
       <c r="E89" t="inlineStr">
         <is>
-          <t>1879.0K</t>
+          <t>219.0K</t>
         </is>
       </c>
       <c r="F89" t="n">
@@ -2352,14 +2344,22 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Philly Fed EmploymentFEB</t>
+          <t>Initial Jobless ClaimsFEB/15</t>
         </is>
       </c>
       <c r="C90" t="inlineStr"/>
-      <c r="D90" t="inlineStr"/>
-      <c r="E90" t="inlineStr"/>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>216K</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>220.0K</t>
+        </is>
+      </c>
       <c r="F90" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="91">
@@ -2370,22 +2370,18 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Philadelphia Fed Manufacturing IndexFEB</t>
+          <t>Continuing Jobless ClaimsFEB/08</t>
         </is>
       </c>
       <c r="C91" t="inlineStr"/>
-      <c r="D91" t="inlineStr">
-        <is>
-          <t>25.5</t>
-        </is>
-      </c>
+      <c r="D91" t="inlineStr"/>
       <c r="E91" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>1879.0K</t>
         </is>
       </c>
       <c r="F91" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="92">
@@ -2396,14 +2392,22 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Philly Fed Prices PaidFEB</t>
+          <t>Philadelphia Fed Manufacturing IndexFEB</t>
         </is>
       </c>
       <c r="C92" t="inlineStr"/>
-      <c r="D92" t="inlineStr"/>
-      <c r="E92" t="inlineStr"/>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>25.5</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
       <c r="F92" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="93">
@@ -2414,16 +2418,12 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageFEB/15</t>
+          <t>Philly Fed Business ConditionsFEB</t>
         </is>
       </c>
       <c r="C93" t="inlineStr"/>
       <c r="D93" t="inlineStr"/>
-      <c r="E93" t="inlineStr">
-        <is>
-          <t>219.0K</t>
-        </is>
-      </c>
+      <c r="E93" t="inlineStr"/>
       <c r="F93" t="n">
         <v>3</v>
       </c>
@@ -2436,7 +2436,7 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Philly Fed Business ConditionsFEB</t>
+          <t>Philly Fed CAPEX IndexFEB</t>
         </is>
       </c>
       <c r="C94" t="inlineStr"/>
@@ -2454,7 +2454,7 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Philly Fed CAPEX IndexFEB</t>
+          <t>Philly Fed New OrdersFEB</t>
         </is>
       </c>
       <c r="C95" t="inlineStr"/>
@@ -2490,12 +2490,16 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Philly Fed New OrdersFEB</t>
+          <t>Jobless Claims 4-week AverageFEB/15</t>
         </is>
       </c>
       <c r="C97" t="inlineStr"/>
       <c r="D97" t="inlineStr"/>
-      <c r="E97" t="inlineStr"/>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>219.0K</t>
+        </is>
+      </c>
       <c r="F97" t="n">
         <v>3</v>
       </c>
@@ -2668,7 +2672,7 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>8-Week Bill Auction</t>
+          <t>4-Week Bill Auction</t>
         </is>
       </c>
       <c r="C106" t="inlineStr"/>
@@ -2686,7 +2690,7 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>4-Week Bill Auction</t>
+          <t>8-Week Bill Auction</t>
         </is>
       </c>
       <c r="C107" t="inlineStr"/>
@@ -2740,14 +2744,14 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeFEB/14</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C110" t="inlineStr"/>
       <c r="D110" t="inlineStr"/>
       <c r="E110" t="inlineStr"/>
       <c r="F110" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="111">
@@ -2794,7 +2798,7 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeFEB/14</t>
+          <t>EIA Distillate Fuel Production ChangeFEB/14</t>
         </is>
       </c>
       <c r="C113" t="inlineStr"/>
@@ -2830,7 +2834,7 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeFEB/14</t>
+          <t>EIA Gasoline Production ChangeFEB/14</t>
         </is>
       </c>
       <c r="C115" t="inlineStr"/>
@@ -2848,14 +2852,14 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeFEB/14</t>
+          <t>EIA Refinery Crude Runs ChangeFEB/14</t>
         </is>
       </c>
       <c r="C116" t="inlineStr"/>
       <c r="D116" t="inlineStr"/>
       <c r="E116" t="inlineStr"/>
       <c r="F116" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="117">
@@ -2866,7 +2870,7 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>15-Year Mortgage RateFEB/20</t>
+          <t>EIA Heating Oil Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C117" t="inlineStr"/>
@@ -2884,7 +2888,7 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeFEB/14</t>
+          <t>EIA Crude Oil Imports ChangeFEB/14</t>
         </is>
       </c>
       <c r="C118" t="inlineStr"/>
@@ -2902,14 +2906,14 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeFEB/14</t>
+          <t>EIA Refinery Crude Runs ChangeFEB/14</t>
         </is>
       </c>
       <c r="C119" t="inlineStr"/>
       <c r="D119" t="inlineStr"/>
       <c r="E119" t="inlineStr"/>
       <c r="F119" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="120">
@@ -2920,7 +2924,7 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>30-Year Mortgage RateFEB/20</t>
+          <t>EIA Gasoline Production ChangeFEB/14</t>
         </is>
       </c>
       <c r="C120" t="inlineStr"/>
@@ -2938,7 +2942,7 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeFEB/14</t>
+          <t>EIA Distillate Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C121" t="inlineStr"/>
@@ -2974,7 +2978,7 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeFEB/14</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C123" t="inlineStr"/>
@@ -2992,7 +2996,7 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeFEB/14</t>
+          <t>EIA Crude Oil Imports ChangeFEB/14</t>
         </is>
       </c>
       <c r="C124" t="inlineStr"/>
@@ -3010,7 +3014,7 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeFEB/14</t>
+          <t>30-Year Mortgage RateFEB/20</t>
         </is>
       </c>
       <c r="C125" t="inlineStr"/>
@@ -3028,7 +3032,7 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeFEB/14</t>
+          <t>15-Year Mortgage RateFEB/20</t>
         </is>
       </c>
       <c r="C126" t="inlineStr"/>
@@ -3046,14 +3050,14 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeFEB/14</t>
+          <t>EIA Gasoline Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C127" t="inlineStr"/>
       <c r="D127" t="inlineStr"/>
       <c r="E127" t="inlineStr"/>
       <c r="F127" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="128">
@@ -3064,14 +3068,14 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeFEB/14</t>
+          <t>EIA Gasoline Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C128" t="inlineStr"/>
       <c r="D128" t="inlineStr"/>
       <c r="E128" t="inlineStr"/>
       <c r="F128" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="129">
@@ -3082,14 +3086,14 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeFEB/14</t>
+          <t>EIA Crude Oil Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C129" t="inlineStr"/>
       <c r="D129" t="inlineStr"/>
       <c r="E129" t="inlineStr"/>
       <c r="F129" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="130">
@@ -3100,7 +3104,7 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeFEB/14</t>
+          <t>EIA Heating Oil Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C130" t="inlineStr"/>
@@ -3298,7 +3302,7 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>S&amp;P Global Services PMI FlashFEB</t>
+          <t>S&amp;P Global Composite PMI FlashFEB</t>
         </is>
       </c>
       <c r="C141" t="inlineStr"/>
@@ -3320,7 +3324,7 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>S&amp;P Global Composite PMI FlashFEB</t>
+          <t>S&amp;P Global Services PMI FlashFEB</t>
         </is>
       </c>
       <c r="C142" t="inlineStr"/>
@@ -3342,14 +3346,14 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>S&amp;P Global Composite PMI FlashFEB</t>
+          <t>S&amp;P Global Manufacturing PMI FlashFEB</t>
         </is>
       </c>
       <c r="C143" t="inlineStr"/>
       <c r="D143" t="inlineStr"/>
       <c r="E143" t="inlineStr">
         <is>
-          <t>52.7</t>
+          <t>51.3</t>
         </is>
       </c>
       <c r="F143" t="n">
@@ -3364,14 +3368,18 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>S&amp;P Global Manufacturing PMI FlashFEB</t>
+          <t>S&amp;P Global Services PMI FlashFEB</t>
         </is>
       </c>
       <c r="C144" t="inlineStr"/>
-      <c r="D144" t="inlineStr"/>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>53.2</t>
+        </is>
+      </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>51.3</t>
+          <t>52.7</t>
         </is>
       </c>
       <c r="F144" t="n">
@@ -3386,14 +3394,14 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>S&amp;P Global Services PMI FlashFEB</t>
+          <t>S&amp;P Global Manufacturing PMI FlashFEB</t>
         </is>
       </c>
       <c r="C145" t="inlineStr"/>
       <c r="D145" t="inlineStr"/>
       <c r="E145" t="inlineStr">
         <is>
-          <t>52.7</t>
+          <t>51.3</t>
         </is>
       </c>
       <c r="F145" t="n">
@@ -3408,14 +3416,14 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>S&amp;P Global Manufacturing PMI FlashFEB</t>
+          <t>S&amp;P Global Composite PMI FlashFEB</t>
         </is>
       </c>
       <c r="C146" t="inlineStr"/>
       <c r="D146" t="inlineStr"/>
       <c r="E146" t="inlineStr">
         <is>
-          <t>51.3</t>
+          <t>52.7</t>
         </is>
       </c>
       <c r="F146" t="n">
@@ -3430,22 +3438,22 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Michigan Inflation Expectations FinalFEB</t>
+          <t>Existing Home SalesJAN</t>
         </is>
       </c>
       <c r="C147" t="inlineStr"/>
       <c r="D147" t="inlineStr">
         <is>
-          <t>4.3%</t>
+          <t>4.17M</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>4.3%</t>
+          <t>4.16M</t>
         </is>
       </c>
       <c r="F147" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="148">
@@ -3456,22 +3464,22 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Existing Home SalesJAN</t>
+          <t>Michigan Consumer Sentiment FinalFEB</t>
         </is>
       </c>
       <c r="C148" t="inlineStr"/>
       <c r="D148" t="inlineStr">
         <is>
-          <t>4.17M</t>
+          <t>67.8</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>4.16M</t>
+          <t>67.8</t>
         </is>
       </c>
       <c r="F148" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="149">
@@ -3482,18 +3490,22 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Existing Home Sales MoMJAN</t>
+          <t>Michigan Consumer Expectations FinalFEB</t>
         </is>
       </c>
       <c r="C149" t="inlineStr"/>
-      <c r="D149" t="inlineStr"/>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>67.3</t>
+        </is>
+      </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>-1.7%</t>
+          <t>67.3</t>
         </is>
       </c>
       <c r="F149" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="150">
@@ -3504,22 +3516,22 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Michigan Consumer Sentiment FinalFEB</t>
+          <t>Michigan Current Conditions FinalFEB</t>
         </is>
       </c>
       <c r="C150" t="inlineStr"/>
       <c r="D150" t="inlineStr">
         <is>
-          <t>67.8</t>
+          <t>68.7</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>67.8</t>
+          <t>68.7</t>
         </is>
       </c>
       <c r="F150" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="151">
@@ -3530,18 +3542,18 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Michigan 5 Year Inflation Expectations FinalFEB</t>
+          <t>Michigan Inflation Expectations FinalFEB</t>
         </is>
       </c>
       <c r="C151" t="inlineStr"/>
       <c r="D151" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>4.3%</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>4.3%</t>
         </is>
       </c>
       <c r="F151" t="n">
@@ -3582,22 +3594,22 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>Michigan Current Conditions FinalFEB</t>
+          <t>Existing Home SalesJAN</t>
         </is>
       </c>
       <c r="C153" t="inlineStr"/>
       <c r="D153" t="inlineStr">
         <is>
-          <t>68.7</t>
+          <t>4.17M</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>68.7</t>
+          <t>4.16M</t>
         </is>
       </c>
       <c r="F153" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="154">
@@ -3608,22 +3620,18 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>Existing Home SalesJAN</t>
+          <t>Existing Home Sales MoMJAN</t>
         </is>
       </c>
       <c r="C154" t="inlineStr"/>
-      <c r="D154" t="inlineStr">
-        <is>
-          <t>4.17M</t>
-        </is>
-      </c>
+      <c r="D154" t="inlineStr"/>
       <c r="E154" t="inlineStr">
         <is>
-          <t>4.16M</t>
+          <t>-1.7%</t>
         </is>
       </c>
       <c r="F154" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="155">
@@ -3634,14 +3642,18 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>Existing Home Sales MoMJAN</t>
+          <t>Michigan Consumer Sentiment FinalFEB</t>
         </is>
       </c>
       <c r="C155" t="inlineStr"/>
-      <c r="D155" t="inlineStr"/>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>67.8</t>
+        </is>
+      </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>-1.7%</t>
+          <t>67.8</t>
         </is>
       </c>
       <c r="F155" t="n">
@@ -3656,22 +3668,22 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>Michigan Consumer Sentiment FinalFEB</t>
+          <t>Michigan 5 Year Inflation Expectations FinalFEB</t>
         </is>
       </c>
       <c r="C156" t="inlineStr"/>
       <c r="D156" t="inlineStr">
         <is>
-          <t>67.8</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>67.8</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="F156" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="157">
@@ -3682,18 +3694,18 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>Michigan 5 Year Inflation Expectations FinalFEB</t>
+          <t>Michigan Current Conditions FinalFEB</t>
         </is>
       </c>
       <c r="C157" t="inlineStr"/>
       <c r="D157" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>68.7</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>68.7</t>
         </is>
       </c>
       <c r="F157" t="n">
@@ -3708,18 +3720,18 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>Michigan Current Conditions FinalFEB</t>
+          <t>Michigan Consumer Expectations FinalFEB</t>
         </is>
       </c>
       <c r="C158" t="inlineStr"/>
       <c r="D158" t="inlineStr">
         <is>
-          <t>68.7</t>
+          <t>67.3</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>68.7</t>
+          <t>67.3</t>
         </is>
       </c>
       <c r="F158" t="n">
@@ -3734,22 +3746,18 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>Michigan Consumer Expectations FinalFEB</t>
+          <t>Existing Home Sales MoMJAN</t>
         </is>
       </c>
       <c r="C159" t="inlineStr"/>
-      <c r="D159" t="inlineStr">
-        <is>
-          <t>67.3</t>
-        </is>
-      </c>
+      <c r="D159" t="inlineStr"/>
       <c r="E159" t="inlineStr">
         <is>
-          <t>67.3</t>
+          <t>-1.7%</t>
         </is>
       </c>
       <c r="F159" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="160">
@@ -3760,18 +3768,18 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>Michigan Consumer Expectations FinalFEB</t>
+          <t>Michigan 5 Year Inflation Expectations FinalFEB</t>
         </is>
       </c>
       <c r="C160" t="inlineStr"/>
       <c r="D160" t="inlineStr">
         <is>
-          <t>67.3</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>67.3</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="F160" t="n">
@@ -3858,7 +3866,7 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>Baker Hughes Oil Rig CountFEB/21</t>
+          <t>Baker Hughes Total Rigs CountFEB/21</t>
         </is>
       </c>
       <c r="C165" t="inlineStr"/>
@@ -3876,7 +3884,7 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>Baker Hughes Total Rigs CountFEB/21</t>
+          <t>Baker Hughes Oil Rig CountFEB/21</t>
         </is>
       </c>
       <c r="C166" t="inlineStr"/>
@@ -3966,7 +3974,7 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>3-Month Bill Auction</t>
+          <t>6-Month Bill Auction</t>
         </is>
       </c>
       <c r="C171" t="inlineStr"/>
@@ -3984,7 +3992,7 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>6-Month Bill Auction</t>
+          <t>3-Month Bill Auction</t>
         </is>
       </c>
       <c r="C172" t="inlineStr"/>
@@ -4002,7 +4010,7 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>6-Month Bill Auction</t>
+          <t>3-Month Bill Auction</t>
         </is>
       </c>
       <c r="C173" t="inlineStr"/>
@@ -4020,7 +4028,7 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>3-Month Bill Auction</t>
+          <t>6-Month Bill Auction</t>
         </is>
       </c>
       <c r="C174" t="inlineStr"/>
@@ -4182,18 +4190,14 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>S&amp;P/Case-Shiller Home Price YoYDEC</t>
+          <t>House Price Index YoYDEC</t>
         </is>
       </c>
       <c r="C183" t="inlineStr"/>
       <c r="D183" t="inlineStr"/>
-      <c r="E183" t="inlineStr">
-        <is>
-          <t>4.2%</t>
-        </is>
-      </c>
+      <c r="E183" t="inlineStr"/>
       <c r="F183" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="184">
@@ -4204,14 +4208,18 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>S&amp;P/Case-Shiller Home Price MoMDEC</t>
+          <t>S&amp;P/Case-Shiller Home Price YoYDEC</t>
         </is>
       </c>
       <c r="C184" t="inlineStr"/>
       <c r="D184" t="inlineStr"/>
-      <c r="E184" t="inlineStr"/>
+      <c r="E184" t="inlineStr">
+        <is>
+          <t>4.2%</t>
+        </is>
+      </c>
       <c r="F184" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="185">
@@ -4262,7 +4270,7 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>House Price Index YoYDEC</t>
+          <t>House Price IndexDEC</t>
         </is>
       </c>
       <c r="C187" t="inlineStr"/>
@@ -4280,7 +4288,7 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>House Price IndexDEC</t>
+          <t>S&amp;P/Case-Shiller Home Price MoMDEC</t>
         </is>
       </c>
       <c r="C188" t="inlineStr"/>
@@ -4370,14 +4378,14 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>Richmond Fed Services Revenues IndexFEB</t>
+          <t>CB Consumer ConfidenceFEB</t>
         </is>
       </c>
       <c r="C193" t="inlineStr"/>
       <c r="D193" t="inlineStr"/>
       <c r="E193" t="inlineStr"/>
       <c r="F193" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="194">
@@ -4388,14 +4396,14 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>CB Consumer ConfidenceFEB</t>
+          <t>Richmond Fed Manufacturing Shipments IndexFEB</t>
         </is>
       </c>
       <c r="C194" t="inlineStr"/>
       <c r="D194" t="inlineStr"/>
       <c r="E194" t="inlineStr"/>
       <c r="F194" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="195">
@@ -4424,7 +4432,7 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>Richmond Fed Manufacturing Shipments IndexFEB</t>
+          <t>Richmond Fed Services Revenues IndexFEB</t>
         </is>
       </c>
       <c r="C196" t="inlineStr"/>
@@ -4514,7 +4522,7 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>5-Year Note Auction</t>
+          <t>Money SupplyJAN</t>
         </is>
       </c>
       <c r="C201" t="inlineStr"/>
@@ -4532,7 +4540,7 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>Money SupplyJAN</t>
+          <t>5-Year Note Auction</t>
         </is>
       </c>
       <c r="C202" t="inlineStr"/>
@@ -4542,6 +4550,42 @@
         <v>3</v>
       </c>
     </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>2025-02-25 13:00:00-05:00</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>5-Year Note Auction</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr"/>
+      <c r="D203" t="inlineStr"/>
+      <c r="E203" t="inlineStr"/>
+      <c r="F203" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>2025-02-25 13:00:00-05:00</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>Money SupplyJAN</t>
+        </is>
+      </c>
+      <c r="C204" t="inlineStr"/>
+      <c r="D204" t="inlineStr"/>
+      <c r="E204" t="inlineStr"/>
+      <c r="F204" t="n">
+        <v>3</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Input_data/EST_US_trad_eco_cal_2025-02-14_to_2025-02-25.xlsx
+++ b/Input_data/EST_US_trad_eco_cal_2025-02-14_to_2025-02-25.xlsx
@@ -864,26 +864,26 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Retail Inventories Ex Autos MoMDEC</t>
+          <t>Business Inventories MoMDEC</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
+          <t>-0.2%</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
           <t>-0.1%</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>0.2%</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>0.2%</t>
-        </is>
-      </c>
       <c r="F16" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="17">
@@ -894,26 +894,26 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Business Inventories MoMDEC</t>
+          <t>Retail Inventories Ex Autos MoMDEC</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>-0.2%</t>
+          <t>-0.1%</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>-0.1%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="18">
@@ -1378,14 +1378,14 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>52-Week Bill Auction</t>
+          <t>Fed Barr Speech</t>
         </is>
       </c>
       <c r="C41" t="inlineStr"/>
       <c r="D41" t="inlineStr"/>
       <c r="E41" t="inlineStr"/>
       <c r="F41" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="42">
@@ -1396,14 +1396,14 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Fed Barr Speech</t>
+          <t>52-Week Bill Auction</t>
         </is>
       </c>
       <c r="C42" t="inlineStr"/>
       <c r="D42" t="inlineStr"/>
       <c r="E42" t="inlineStr"/>
       <c r="F42" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="43">
@@ -1472,14 +1472,14 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Net Long-term TIC FlowsDEC</t>
+          <t>Foreign Bond InvestmentDEC</t>
         </is>
       </c>
       <c r="C46" t="inlineStr"/>
       <c r="D46" t="inlineStr"/>
       <c r="E46" t="inlineStr"/>
       <c r="F46" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="47">
@@ -1490,14 +1490,14 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Foreign Bond InvestmentDEC</t>
+          <t>Net Long-term TIC FlowsDEC</t>
         </is>
       </c>
       <c r="C47" t="inlineStr"/>
       <c r="D47" t="inlineStr"/>
       <c r="E47" t="inlineStr"/>
       <c r="F47" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="48">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>MBA Purchase IndexFEB/14</t>
+          <t>MBA Mortgage Refinance IndexFEB/14</t>
         </is>
       </c>
       <c r="C55" t="inlineStr"/>
@@ -1652,7 +1652,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>MBA Mortgage Refinance IndexFEB/14</t>
+          <t>MBA Purchase IndexFEB/14</t>
         </is>
       </c>
       <c r="C56" t="inlineStr"/>
@@ -2322,14 +2322,22 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Philly Fed Business ConditionsFEB</t>
+          <t>Philadelphia Fed Manufacturing IndexFEB</t>
         </is>
       </c>
       <c r="C89" t="inlineStr"/>
-      <c r="D89" t="inlineStr"/>
-      <c r="E89" t="inlineStr"/>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>25.5</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
       <c r="F89" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="90">
@@ -2340,22 +2348,14 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsFEB/15</t>
+          <t>Philly Fed Business ConditionsFEB</t>
         </is>
       </c>
       <c r="C90" t="inlineStr"/>
-      <c r="D90" t="inlineStr">
-        <is>
-          <t>216K</t>
-        </is>
-      </c>
-      <c r="E90" t="inlineStr">
-        <is>
-          <t>220.0K</t>
-        </is>
-      </c>
+      <c r="D90" t="inlineStr"/>
+      <c r="E90" t="inlineStr"/>
       <c r="F90" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="91">
@@ -2366,18 +2366,22 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsFEB/08</t>
+          <t>Initial Jobless ClaimsFEB/15</t>
         </is>
       </c>
       <c r="C91" t="inlineStr"/>
-      <c r="D91" t="inlineStr"/>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>216K</t>
+        </is>
+      </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>1879.0K</t>
+          <t>220.0K</t>
         </is>
       </c>
       <c r="F91" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="92">
@@ -2388,22 +2392,18 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Philadelphia Fed Manufacturing IndexFEB</t>
+          <t>Continuing Jobless ClaimsFEB/08</t>
         </is>
       </c>
       <c r="C92" t="inlineStr"/>
-      <c r="D92" t="inlineStr">
-        <is>
-          <t>25.5</t>
-        </is>
-      </c>
+      <c r="D92" t="inlineStr"/>
       <c r="E92" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>1879.0K</t>
         </is>
       </c>
       <c r="F92" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="93">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeFEB/14</t>
+          <t>EIA Distillate Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C109" t="inlineStr"/>
@@ -2744,7 +2744,7 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeFEB/14</t>
+          <t>EIA Distillate Fuel Production ChangeFEB/14</t>
         </is>
       </c>
       <c r="C110" t="inlineStr"/>
@@ -2762,7 +2762,7 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeFEB/14</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C111" t="inlineStr"/>
@@ -2780,7 +2780,7 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeFEB/14</t>
+          <t>EIA Crude Oil Imports ChangeFEB/14</t>
         </is>
       </c>
       <c r="C112" t="inlineStr"/>
@@ -2798,7 +2798,7 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeFEB/14</t>
+          <t>30-Year Mortgage RateFEB/20</t>
         </is>
       </c>
       <c r="C113" t="inlineStr"/>
@@ -2816,7 +2816,7 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>30-Year Mortgage RateFEB/20</t>
+          <t>15-Year Mortgage RateFEB/20</t>
         </is>
       </c>
       <c r="C114" t="inlineStr"/>
@@ -2834,7 +2834,7 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>15-Year Mortgage RateFEB/20</t>
+          <t>EIA Refinery Crude Runs ChangeFEB/14</t>
         </is>
       </c>
       <c r="C115" t="inlineStr"/>
@@ -3050,7 +3050,7 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeFEB/14</t>
+          <t>EIA Gasoline Production ChangeFEB/14</t>
         </is>
       </c>
       <c r="C127" t="inlineStr"/>
@@ -4014,7 +4014,7 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>6-Month Bill Auction</t>
+          <t>3-Month Bill Auction</t>
         </is>
       </c>
       <c r="C173" t="inlineStr"/>
@@ -4032,7 +4032,7 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>3-Month Bill Auction</t>
+          <t>6-Month Bill Auction</t>
         </is>
       </c>
       <c r="C174" t="inlineStr"/>
@@ -4176,7 +4176,7 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>S&amp;P/Case-Shiller Home Price MoMDEC</t>
+          <t>House Price Index YoYDEC</t>
         </is>
       </c>
       <c r="C182" t="inlineStr"/>
@@ -4292,7 +4292,7 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>House Price Index YoYDEC</t>
+          <t>S&amp;P/Case-Shiller Home Price MoMDEC</t>
         </is>
       </c>
       <c r="C188" t="inlineStr"/>
@@ -4382,7 +4382,7 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>Richmond Fed Manufacturing Shipments IndexFEB</t>
+          <t>Richmond Fed Services Revenues IndexFEB</t>
         </is>
       </c>
       <c r="C193" t="inlineStr"/>
@@ -4400,14 +4400,14 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>Richmond Fed Services Revenues IndexFEB</t>
+          <t>CB Consumer ConfidenceFEB</t>
         </is>
       </c>
       <c r="C194" t="inlineStr"/>
       <c r="D194" t="inlineStr"/>
       <c r="E194" t="inlineStr"/>
       <c r="F194" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="195">
@@ -4436,14 +4436,14 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>CB Consumer ConfidenceFEB</t>
+          <t>Richmond Fed Manufacturing Shipments IndexFEB</t>
         </is>
       </c>
       <c r="C196" t="inlineStr"/>
       <c r="D196" t="inlineStr"/>
       <c r="E196" t="inlineStr"/>
       <c r="F196" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="197">

--- a/Input_data/EST_US_trad_eco_cal_2025-02-14_to_2025-02-25.xlsx
+++ b/Input_data/EST_US_trad_eco_cal_2025-02-14_to_2025-02-25.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F204"/>
+  <dimension ref="A1:F205"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -864,26 +864,26 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Business Inventories MoMDEC</t>
+          <t>Retail Inventories Ex Autos MoMDEC</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>-0.2%</t>
+          <t>-0.1%</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>-0.1%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="17">
@@ -894,26 +894,26 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Retail Inventories Ex Autos MoMDEC</t>
+          <t>Business Inventories MoMDEC</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
+          <t>-0.2%</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
           <t>-0.1%</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>0.2%</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>0.2%</t>
-        </is>
-      </c>
       <c r="F17" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="18">
@@ -1378,14 +1378,14 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Fed Barr Speech</t>
+          <t>52-Week Bill Auction</t>
         </is>
       </c>
       <c r="C41" t="inlineStr"/>
       <c r="D41" t="inlineStr"/>
       <c r="E41" t="inlineStr"/>
       <c r="F41" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="42">
@@ -1396,14 +1396,14 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>52-Week Bill Auction</t>
+          <t>Fed Barr Speech</t>
         </is>
       </c>
       <c r="C42" t="inlineStr"/>
       <c r="D42" t="inlineStr"/>
       <c r="E42" t="inlineStr"/>
       <c r="F42" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="43">
@@ -1472,14 +1472,14 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Foreign Bond InvestmentDEC</t>
+          <t>Net Long-term TIC FlowsDEC</t>
         </is>
       </c>
       <c r="C46" t="inlineStr"/>
       <c r="D46" t="inlineStr"/>
       <c r="E46" t="inlineStr"/>
       <c r="F46" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="47">
@@ -1490,14 +1490,14 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Net Long-term TIC FlowsDEC</t>
+          <t>Foreign Bond InvestmentDEC</t>
         </is>
       </c>
       <c r="C47" t="inlineStr"/>
       <c r="D47" t="inlineStr"/>
       <c r="E47" t="inlineStr"/>
       <c r="F47" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="48">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>MBA Mortgage Refinance IndexFEB/14</t>
+          <t>MBA Purchase IndexFEB/14</t>
         </is>
       </c>
       <c r="C55" t="inlineStr"/>
@@ -1652,7 +1652,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>MBA Purchase IndexFEB/14</t>
+          <t>MBA Mortgage Refinance IndexFEB/14</t>
         </is>
       </c>
       <c r="C56" t="inlineStr"/>
@@ -2322,22 +2322,18 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Philadelphia Fed Manufacturing IndexFEB</t>
+          <t>Continuing Jobless ClaimsFEB/08</t>
         </is>
       </c>
       <c r="C89" t="inlineStr"/>
-      <c r="D89" t="inlineStr">
-        <is>
-          <t>25.5</t>
-        </is>
-      </c>
+      <c r="D89" t="inlineStr"/>
       <c r="E89" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>1879.0K</t>
         </is>
       </c>
       <c r="F89" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="90">
@@ -2348,14 +2344,22 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Philly Fed Business ConditionsFEB</t>
+          <t>Philadelphia Fed Manufacturing IndexFEB</t>
         </is>
       </c>
       <c r="C90" t="inlineStr"/>
-      <c r="D90" t="inlineStr"/>
-      <c r="E90" t="inlineStr"/>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>25.5</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
       <c r="F90" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="91">
@@ -2366,22 +2370,14 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsFEB/15</t>
+          <t>Philly Fed Business ConditionsFEB</t>
         </is>
       </c>
       <c r="C91" t="inlineStr"/>
-      <c r="D91" t="inlineStr">
-        <is>
-          <t>216K</t>
-        </is>
-      </c>
-      <c r="E91" t="inlineStr">
-        <is>
-          <t>220.0K</t>
-        </is>
-      </c>
+      <c r="D91" t="inlineStr"/>
+      <c r="E91" t="inlineStr"/>
       <c r="F91" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="92">
@@ -2392,18 +2388,22 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsFEB/08</t>
+          <t>Initial Jobless ClaimsFEB/15</t>
         </is>
       </c>
       <c r="C92" t="inlineStr"/>
-      <c r="D92" t="inlineStr"/>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>216K</t>
+        </is>
+      </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>1879.0K</t>
+          <t>220.0K</t>
         </is>
       </c>
       <c r="F92" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="93">
@@ -2834,7 +2834,7 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeFEB/14</t>
+          <t>EIA Gasoline Production ChangeFEB/14</t>
         </is>
       </c>
       <c r="C115" t="inlineStr"/>
@@ -3050,7 +3050,7 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeFEB/14</t>
+          <t>EIA Refinery Crude Runs ChangeFEB/14</t>
         </is>
       </c>
       <c r="C127" t="inlineStr"/>
@@ -4014,7 +4014,7 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>3-Month Bill Auction</t>
+          <t>6-Month Bill Auction</t>
         </is>
       </c>
       <c r="C173" t="inlineStr"/>
@@ -4032,7 +4032,7 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>6-Month Bill Auction</t>
+          <t>3-Month Bill Auction</t>
         </is>
       </c>
       <c r="C174" t="inlineStr"/>
@@ -4176,7 +4176,7 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>House Price Index YoYDEC</t>
+          <t>S&amp;P/Case-Shiller Home Price MoMDEC</t>
         </is>
       </c>
       <c r="C182" t="inlineStr"/>
@@ -4292,7 +4292,7 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>S&amp;P/Case-Shiller Home Price MoMDEC</t>
+          <t>House Price Index YoYDEC</t>
         </is>
       </c>
       <c r="C188" t="inlineStr"/>
@@ -4382,7 +4382,7 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>Richmond Fed Services Revenues IndexFEB</t>
+          <t>Richmond Fed Manufacturing IndexFEB</t>
         </is>
       </c>
       <c r="C193" t="inlineStr"/>
@@ -4400,14 +4400,14 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>CB Consumer ConfidenceFEB</t>
+          <t>Richmond Fed Manufacturing Shipments IndexFEB</t>
         </is>
       </c>
       <c r="C194" t="inlineStr"/>
       <c r="D194" t="inlineStr"/>
       <c r="E194" t="inlineStr"/>
       <c r="F194" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="195">
@@ -4418,14 +4418,14 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>Richmond Fed Manufacturing IndexFEB</t>
+          <t>CB Consumer ConfidenceFEB</t>
         </is>
       </c>
       <c r="C195" t="inlineStr"/>
       <c r="D195" t="inlineStr"/>
       <c r="E195" t="inlineStr"/>
       <c r="F195" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="196">
@@ -4436,7 +4436,7 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>Richmond Fed Manufacturing Shipments IndexFEB</t>
+          <t>Richmond Fed Services Revenues IndexFEB</t>
         </is>
       </c>
       <c r="C196" t="inlineStr"/>
@@ -4562,7 +4562,7 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>5-Year Note Auction</t>
+          <t>Money SupplyJAN</t>
         </is>
       </c>
       <c r="C203" t="inlineStr"/>
@@ -4580,7 +4580,7 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>Money SupplyJAN</t>
+          <t>5-Year Note Auction</t>
         </is>
       </c>
       <c r="C204" t="inlineStr"/>
@@ -4590,6 +4590,24 @@
         <v>3</v>
       </c>
     </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>2025-02-25 16:30:00-05:00</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>API Crude Oil Stock ChangeFEB/21</t>
+        </is>
+      </c>
+      <c r="C205" t="inlineStr"/>
+      <c r="D205" t="inlineStr"/>
+      <c r="E205" t="inlineStr"/>
+      <c r="F205" t="n">
+        <v>2</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
